--- a/ЛР4_Пять_сил_Портера/Excel/ЛР4_1_конкуренция_и_барьеры_входа_TableMind.xlsx
+++ b/ЛР4_Пять_сил_Портера/Excel/ЛР4_1_конкуренция_и_барьеры_входа_TableMind.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-3ab569\ЛР4_Пять_сил_Портера\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР4_Пять_сил_Портера\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5FCE24-13E0-4909-A8F7-DA0681467E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5C84AC7-77B7-485C-BE0E-026816F4A84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="09_Источники" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1236,9 +1237,6 @@
     <t>частичный конкурент: AI-агент для Excel</t>
   </si>
   <si>
-    <t>Similarweb Pro, 06-08.2026, 03.10.2026; брендовый поиск - ДОСНЯТЬ</t>
-  </si>
-  <si>
     <t>perfectxl.com</t>
   </si>
   <si>
@@ -1299,9 +1297,6 @@
     <t>Google Trends (индекс 0-100, ЛР1)</t>
   </si>
   <si>
-    <t>CPC, PPC, SEO difficulty, выдача и объявления: ДОСНЯТЬ (Semrush, Google Ads)</t>
-  </si>
-  <si>
     <t>spreadsheet audit</t>
   </si>
   <si>
@@ -1365,12 +1360,6 @@
     <t>G2: CIMCON Software (EUC-риск)</t>
   </si>
   <si>
-    <t>Среднее число отзывов на конкурента (G2, Capterra, Trustpilot); отзывы Google, кейсы и возраст бренда - ДОСНЯТЬ</t>
-  </si>
-  <si>
-    <t>D и E - экспертные баллы (Д-17); финансирование, штат, вакансии, объявления - ДОСНЯТЬ (Crunchbase, LinkedIn)</t>
-  </si>
-  <si>
     <t>CPC, PPC, SEO difficulty (при отсутствии - прокси: органика и платный поиск Similarweb к порогам)</t>
   </si>
   <si>
@@ -1381,6 +1370,18 @@
   </si>
   <si>
     <t>Интегральная оценка давления (сумма весов в шаблоне 1,04, поэтому делится на сумму весов).</t>
+  </si>
+  <si>
+    <t>Similarweb Pro, 06-08.2026, 03.10.2026; брендовый поиск - доля прямых заходов как прокси</t>
+  </si>
+  <si>
+    <t>CPC, PPC, SEO difficulty, выдача и объявления: модельные показатели (отчет ЛР4, приложение Д, допущение Д-33)</t>
+  </si>
+  <si>
+    <t>Среднее число отзывов на конкурента (G2, Capterra, Trustpilot); отзывы Google, кейсы и возраст бренда - по сайтам конкурентов</t>
+  </si>
+  <si>
+    <t>D и E - экспертные баллы (Д-17); финансирование и штат - по открытым источникам (ЛР5, приложение Д)</t>
   </si>
 </sst>
 </file>
@@ -1537,6 +1538,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1551,9 +1555,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2108,30 +2109,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
     </row>
     <row r="4" spans="1:9" ht="17" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -2304,63 +2305,63 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14" customHeight="1">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="27"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="27"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2388,26 +2389,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -2448,7 +2449,7 @@
       <c r="E4" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="24">
         <v>46298</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -2471,7 +2472,7 @@
       <c r="E5" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="24">
         <v>46298</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -2494,7 +2495,7 @@
       <c r="E6" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="24">
         <v>46298</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -2517,7 +2518,7 @@
       <c r="E7" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="24">
         <v>46298</v>
       </c>
       <c r="G7" s="2" t="s">
@@ -2540,7 +2541,7 @@
       <c r="E8" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="24">
         <v>46298</v>
       </c>
       <c r="G8" s="2" t="s">
@@ -2563,7 +2564,7 @@
       <c r="E9" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="24">
         <v>46298</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -2586,7 +2587,7 @@
       <c r="E10" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="24">
         <v>46298</v>
       </c>
       <c r="G10" s="2" t="s">
@@ -2609,7 +2610,7 @@
       <c r="E11" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="24">
         <v>46298</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -2632,7 +2633,7 @@
       <c r="E12" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="24">
         <v>46298</v>
       </c>
       <c r="G12" s="2" t="s">
@@ -2655,7 +2656,7 @@
       <c r="E13" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="24">
         <v>46298</v>
       </c>
       <c r="G13" s="2" t="s">
@@ -2678,7 +2679,7 @@
       <c r="E14" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="24">
         <v>46298</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -2701,7 +2702,7 @@
       <c r="E15" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="24">
         <v>46298</v>
       </c>
       <c r="G15" s="2" t="s">
@@ -2724,7 +2725,7 @@
       <c r="E16" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="24">
         <v>46298</v>
       </c>
       <c r="G16" s="2" t="s">
@@ -2747,7 +2748,7 @@
       <c r="E17" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="24">
         <v>46298</v>
       </c>
       <c r="G17" s="2" t="s">
@@ -2770,7 +2771,7 @@
       <c r="E18" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="24">
         <v>46298</v>
       </c>
       <c r="G18" s="2" t="s">
@@ -2793,7 +2794,7 @@
       <c r="E19" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="24">
         <v>46298</v>
       </c>
       <c r="G19" s="2" t="s">
@@ -2825,24 +2826,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="4" spans="1:6" ht="17" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -3145,46 +3146,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="16.05" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="3" spans="1:17" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -3239,7 +3240,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="40.5">
+    <row r="4" spans="1:17" ht="54">
       <c r="A4" s="4" t="s">
         <v>395</v>
       </c>
@@ -3287,15 +3288,15 @@
       </c>
       <c r="P4" s="11"/>
       <c r="Q4" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="54">
+      <c r="A5" s="4" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="40.5">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>399</v>
       </c>
       <c r="C5" s="10">
         <v>35325</v>
@@ -3340,15 +3341,15 @@
       </c>
       <c r="P5" s="11"/>
       <c r="Q5" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="40.5">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="54">
       <c r="A6" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>401</v>
       </c>
       <c r="C6" s="10">
         <v>241737</v>
@@ -3393,15 +3394,15 @@
       </c>
       <c r="P6" s="11"/>
       <c r="Q6" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="40.5">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="54">
       <c r="A7" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>403</v>
       </c>
       <c r="C7" s="10">
         <v>202178</v>
@@ -3446,15 +3447,15 @@
       </c>
       <c r="P7" s="11"/>
       <c r="Q7" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="40.5">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="54">
       <c r="A8" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>405</v>
       </c>
       <c r="C8" s="10">
         <v>14688</v>
@@ -3499,15 +3500,15 @@
       </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="40.5">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="54">
       <c r="A9" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C9" s="10">
         <v>17824</v>
@@ -3552,15 +3553,15 @@
       </c>
       <c r="P9" s="11"/>
       <c r="Q9" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="40.5">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="54">
       <c r="A10" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C10" s="10">
         <v>292214</v>
@@ -3605,15 +3606,15 @@
       </c>
       <c r="P10" s="11"/>
       <c r="Q10" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="40.5">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="54">
       <c r="A11" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C11" s="10">
         <v>116617</v>
@@ -3658,15 +3659,15 @@
       </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="40.5">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="54">
       <c r="A12" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>410</v>
       </c>
       <c r="C12" s="10">
         <v>222359</v>
@@ -3711,15 +3712,15 @@
       </c>
       <c r="P12" s="11"/>
       <c r="Q12" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="40.5">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="54">
       <c r="A13" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="C13" s="10">
         <v>701540</v>
@@ -3764,15 +3765,15 @@
       </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="40.5">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="54">
       <c r="A14" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C14" s="10">
         <v>1935</v>
@@ -3817,15 +3818,15 @@
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="40.5">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="54">
       <c r="A15" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>415</v>
       </c>
       <c r="C15" s="10">
         <v>5522</v>
@@ -3870,7 +3871,7 @@
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="4" t="s">
-        <v>397</v>
+        <v>442</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -4427,30 +4428,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:9" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -4742,38 +4743,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
     </row>
     <row r="2" spans="1:13" ht="16.05" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
     </row>
     <row r="3" spans="1:13" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -4786,7 +4787,7 @@
         <v>133</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>177</v>
@@ -4816,15 +4817,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54">
+    <row r="4" spans="1:13" ht="67.5">
       <c r="A4" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>184</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D4" s="10">
         <v>47.6</v>
@@ -4836,26 +4837,26 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="9" t="str">
-        <f>IF(COUNT(E4:J4)&lt;2,"",MIN(1,(IF(ISNUMBER(E4),MIN(E4/2,1),0)+IF(ISNUMBER(F4),F4,0)+IF(ISNUMBER(G4),G4/100,0)+IF(ISNUMBER(H4),MIN(H4/10,1),0)+IF(ISNUMBER(J4),MIN(J4/50,1),0))/MAX(1,COUNT(E4:H4,J4))))</f>
+        <f t="shared" ref="K4:K33" si="0">IF(COUNT(E4:J4)&lt;2,"",MIN(1,(IF(ISNUMBER(E4),MIN(E4/2,1),0)+IF(ISNUMBER(F4),F4,0)+IF(ISNUMBER(G4),G4/100,0)+IF(ISNUMBER(H4),MIN(H4/10,1),0)+IF(ISNUMBER(J4),MIN(J4/50,1),0))/MAX(1,COUNT(E4:H4,J4))))</f>
         <v/>
       </c>
       <c r="L4" s="18" t="str">
-        <f>IF(K4="","",IF(K4&gt;=0.7,5,IF(K4&gt;=0.4,3,1)))</f>
+        <f t="shared" ref="L4:L33" si="1">IF(K4="","",IF(K4&gt;=0.7,5,IF(K4&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M4" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="54">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="67.5">
       <c r="A5" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>184</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D5" s="10">
         <v>32</v>
@@ -4867,26 +4868,26 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="9" t="str">
-        <f>IF(COUNT(E5:J5)&lt;2,"",MIN(1,(IF(ISNUMBER(E5),MIN(E5/2,1),0)+IF(ISNUMBER(F5),F5,0)+IF(ISNUMBER(G5),G5/100,0)+IF(ISNUMBER(H5),MIN(H5/10,1),0)+IF(ISNUMBER(J5),MIN(J5/50,1),0))/MAX(1,COUNT(E5:H5,J5))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L5" s="18" t="str">
-        <f>IF(K5="","",IF(K5&gt;=0.7,5,IF(K5&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M5" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="67.5">
+      <c r="A6" s="4" t="s">
         <v>418</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="54">
-      <c r="A6" s="4" t="s">
-        <v>420</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>185</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D6" s="10">
         <v>13.2</v>
@@ -4898,26 +4899,26 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="9" t="str">
-        <f>IF(COUNT(E6:J6)&lt;2,"",MIN(1,(IF(ISNUMBER(E6),MIN(E6/2,1),0)+IF(ISNUMBER(F6),F6,0)+IF(ISNUMBER(G6),G6/100,0)+IF(ISNUMBER(H6),MIN(H6/10,1),0)+IF(ISNUMBER(J6),MIN(J6/50,1),0))/MAX(1,COUNT(E6:H6,J6))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L6" s="18" t="str">
-        <f>IF(K6="","",IF(K6&gt;=0.7,5,IF(K6&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M6" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="54">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="67.5">
       <c r="A7" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>184</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D7" s="10">
         <v>29</v>
@@ -4929,26 +4930,26 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="9" t="str">
-        <f>IF(COUNT(E7:J7)&lt;2,"",MIN(1,(IF(ISNUMBER(E7),MIN(E7/2,1),0)+IF(ISNUMBER(F7),F7,0)+IF(ISNUMBER(G7),G7/100,0)+IF(ISNUMBER(H7),MIN(H7/10,1),0)+IF(ISNUMBER(J7),MIN(J7/50,1),0))/MAX(1,COUNT(E7:H7,J7))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L7" s="18" t="str">
-        <f>IF(K7="","",IF(K7&gt;=0.7,5,IF(K7&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M7" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="54">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="67.5">
       <c r="A8" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D8" s="10">
         <v>60.9</v>
@@ -4960,26 +4961,26 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="9" t="str">
-        <f>IF(COUNT(E8:J8)&lt;2,"",MIN(1,(IF(ISNUMBER(E8),MIN(E8/2,1),0)+IF(ISNUMBER(F8),F8,0)+IF(ISNUMBER(G8),G8/100,0)+IF(ISNUMBER(H8),MIN(H8/10,1),0)+IF(ISNUMBER(J8),MIN(J8/50,1),0))/MAX(1,COUNT(E8:H8,J8))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L8" s="18" t="str">
-        <f>IF(K8="","",IF(K8&gt;=0.7,5,IF(K8&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M8" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="54">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="67.5">
       <c r="A9" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D9" s="10">
         <v>0.6</v>
@@ -4991,15 +4992,15 @@
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="9" t="str">
-        <f>IF(COUNT(E9:J9)&lt;2,"",MIN(1,(IF(ISNUMBER(E9),MIN(E9/2,1),0)+IF(ISNUMBER(F9),F9,0)+IF(ISNUMBER(G9),G9/100,0)+IF(ISNUMBER(H9),MIN(H9/10,1),0)+IF(ISNUMBER(J9),MIN(J9/50,1),0))/MAX(1,COUNT(E9:H9,J9))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L9" s="18" t="str">
-        <f>IF(K9="","",IF(K9&gt;=0.7,5,IF(K9&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M9" s="2" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5014,11 +5015,11 @@
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="9" t="str">
-        <f>IF(COUNT(E10:J10)&lt;2,"",MIN(1,(IF(ISNUMBER(E10),MIN(E10/2,1),0)+IF(ISNUMBER(F10),F10,0)+IF(ISNUMBER(G10),G10/100,0)+IF(ISNUMBER(H10),MIN(H10/10,1),0)+IF(ISNUMBER(J10),MIN(J10/50,1),0))/MAX(1,COUNT(E10:H10,J10))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L10" s="18" t="str">
-        <f>IF(K10="","",IF(K10&gt;=0.7,5,IF(K10&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M10" s="2"/>
@@ -5035,11 +5036,11 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="9" t="str">
-        <f>IF(COUNT(E11:J11)&lt;2,"",MIN(1,(IF(ISNUMBER(E11),MIN(E11/2,1),0)+IF(ISNUMBER(F11),F11,0)+IF(ISNUMBER(G11),G11/100,0)+IF(ISNUMBER(H11),MIN(H11/10,1),0)+IF(ISNUMBER(J11),MIN(J11/50,1),0))/MAX(1,COUNT(E11:H11,J11))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L11" s="18" t="str">
-        <f>IF(K11="","",IF(K11&gt;=0.7,5,IF(K11&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M11" s="2"/>
@@ -5056,11 +5057,11 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="9" t="str">
-        <f>IF(COUNT(E12:J12)&lt;2,"",MIN(1,(IF(ISNUMBER(E12),MIN(E12/2,1),0)+IF(ISNUMBER(F12),F12,0)+IF(ISNUMBER(G12),G12/100,0)+IF(ISNUMBER(H12),MIN(H12/10,1),0)+IF(ISNUMBER(J12),MIN(J12/50,1),0))/MAX(1,COUNT(E12:H12,J12))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L12" s="18" t="str">
-        <f>IF(K12="","",IF(K12&gt;=0.7,5,IF(K12&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M12" s="2"/>
@@ -5077,11 +5078,11 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="9" t="str">
-        <f>IF(COUNT(E13:J13)&lt;2,"",MIN(1,(IF(ISNUMBER(E13),MIN(E13/2,1),0)+IF(ISNUMBER(F13),F13,0)+IF(ISNUMBER(G13),G13/100,0)+IF(ISNUMBER(H13),MIN(H13/10,1),0)+IF(ISNUMBER(J13),MIN(J13/50,1),0))/MAX(1,COUNT(E13:H13,J13))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L13" s="18" t="str">
-        <f>IF(K13="","",IF(K13&gt;=0.7,5,IF(K13&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M13" s="2"/>
@@ -5098,11 +5099,11 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="9" t="str">
-        <f>IF(COUNT(E14:J14)&lt;2,"",MIN(1,(IF(ISNUMBER(E14),MIN(E14/2,1),0)+IF(ISNUMBER(F14),F14,0)+IF(ISNUMBER(G14),G14/100,0)+IF(ISNUMBER(H14),MIN(H14/10,1),0)+IF(ISNUMBER(J14),MIN(J14/50,1),0))/MAX(1,COUNT(E14:H14,J14))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L14" s="18" t="str">
-        <f>IF(K14="","",IF(K14&gt;=0.7,5,IF(K14&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M14" s="2"/>
@@ -5119,11 +5120,11 @@
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="9" t="str">
-        <f>IF(COUNT(E15:J15)&lt;2,"",MIN(1,(IF(ISNUMBER(E15),MIN(E15/2,1),0)+IF(ISNUMBER(F15),F15,0)+IF(ISNUMBER(G15),G15/100,0)+IF(ISNUMBER(H15),MIN(H15/10,1),0)+IF(ISNUMBER(J15),MIN(J15/50,1),0))/MAX(1,COUNT(E15:H15,J15))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L15" s="18" t="str">
-        <f>IF(K15="","",IF(K15&gt;=0.7,5,IF(K15&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M15" s="2"/>
@@ -5140,11 +5141,11 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="9" t="str">
-        <f>IF(COUNT(E16:J16)&lt;2,"",MIN(1,(IF(ISNUMBER(E16),MIN(E16/2,1),0)+IF(ISNUMBER(F16),F16,0)+IF(ISNUMBER(G16),G16/100,0)+IF(ISNUMBER(H16),MIN(H16/10,1),0)+IF(ISNUMBER(J16),MIN(J16/50,1),0))/MAX(1,COUNT(E16:H16,J16))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L16" s="18" t="str">
-        <f>IF(K16="","",IF(K16&gt;=0.7,5,IF(K16&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M16" s="2"/>
@@ -5161,11 +5162,11 @@
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="9" t="str">
-        <f>IF(COUNT(E17:J17)&lt;2,"",MIN(1,(IF(ISNUMBER(E17),MIN(E17/2,1),0)+IF(ISNUMBER(F17),F17,0)+IF(ISNUMBER(G17),G17/100,0)+IF(ISNUMBER(H17),MIN(H17/10,1),0)+IF(ISNUMBER(J17),MIN(J17/50,1),0))/MAX(1,COUNT(E17:H17,J17))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L17" s="18" t="str">
-        <f>IF(K17="","",IF(K17&gt;=0.7,5,IF(K17&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M17" s="2"/>
@@ -5182,11 +5183,11 @@
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="9" t="str">
-        <f>IF(COUNT(E18:J18)&lt;2,"",MIN(1,(IF(ISNUMBER(E18),MIN(E18/2,1),0)+IF(ISNUMBER(F18),F18,0)+IF(ISNUMBER(G18),G18/100,0)+IF(ISNUMBER(H18),MIN(H18/10,1),0)+IF(ISNUMBER(J18),MIN(J18/50,1),0))/MAX(1,COUNT(E18:H18,J18))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L18" s="18" t="str">
-        <f>IF(K18="","",IF(K18&gt;=0.7,5,IF(K18&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M18" s="2"/>
@@ -5203,11 +5204,11 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="9" t="str">
-        <f>IF(COUNT(E19:J19)&lt;2,"",MIN(1,(IF(ISNUMBER(E19),MIN(E19/2,1),0)+IF(ISNUMBER(F19),F19,0)+IF(ISNUMBER(G19),G19/100,0)+IF(ISNUMBER(H19),MIN(H19/10,1),0)+IF(ISNUMBER(J19),MIN(J19/50,1),0))/MAX(1,COUNT(E19:H19,J19))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L19" s="18" t="str">
-        <f>IF(K19="","",IF(K19&gt;=0.7,5,IF(K19&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M19" s="2"/>
@@ -5224,11 +5225,11 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="9" t="str">
-        <f>IF(COUNT(E20:J20)&lt;2,"",MIN(1,(IF(ISNUMBER(E20),MIN(E20/2,1),0)+IF(ISNUMBER(F20),F20,0)+IF(ISNUMBER(G20),G20/100,0)+IF(ISNUMBER(H20),MIN(H20/10,1),0)+IF(ISNUMBER(J20),MIN(J20/50,1),0))/MAX(1,COUNT(E20:H20,J20))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L20" s="18" t="str">
-        <f>IF(K20="","",IF(K20&gt;=0.7,5,IF(K20&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M20" s="2"/>
@@ -5245,11 +5246,11 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="9" t="str">
-        <f>IF(COUNT(E21:J21)&lt;2,"",MIN(1,(IF(ISNUMBER(E21),MIN(E21/2,1),0)+IF(ISNUMBER(F21),F21,0)+IF(ISNUMBER(G21),G21/100,0)+IF(ISNUMBER(H21),MIN(H21/10,1),0)+IF(ISNUMBER(J21),MIN(J21/50,1),0))/MAX(1,COUNT(E21:H21,J21))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L21" s="18" t="str">
-        <f>IF(K21="","",IF(K21&gt;=0.7,5,IF(K21&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M21" s="2"/>
@@ -5266,11 +5267,11 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="9" t="str">
-        <f>IF(COUNT(E22:J22)&lt;2,"",MIN(1,(IF(ISNUMBER(E22),MIN(E22/2,1),0)+IF(ISNUMBER(F22),F22,0)+IF(ISNUMBER(G22),G22/100,0)+IF(ISNUMBER(H22),MIN(H22/10,1),0)+IF(ISNUMBER(J22),MIN(J22/50,1),0))/MAX(1,COUNT(E22:H22,J22))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L22" s="18" t="str">
-        <f>IF(K22="","",IF(K22&gt;=0.7,5,IF(K22&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M22" s="2"/>
@@ -5287,11 +5288,11 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="9" t="str">
-        <f>IF(COUNT(E23:J23)&lt;2,"",MIN(1,(IF(ISNUMBER(E23),MIN(E23/2,1),0)+IF(ISNUMBER(F23),F23,0)+IF(ISNUMBER(G23),G23/100,0)+IF(ISNUMBER(H23),MIN(H23/10,1),0)+IF(ISNUMBER(J23),MIN(J23/50,1),0))/MAX(1,COUNT(E23:H23,J23))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L23" s="18" t="str">
-        <f>IF(K23="","",IF(K23&gt;=0.7,5,IF(K23&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M23" s="2"/>
@@ -5308,11 +5309,11 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="9" t="str">
-        <f>IF(COUNT(E24:J24)&lt;2,"",MIN(1,(IF(ISNUMBER(E24),MIN(E24/2,1),0)+IF(ISNUMBER(F24),F24,0)+IF(ISNUMBER(G24),G24/100,0)+IF(ISNUMBER(H24),MIN(H24/10,1),0)+IF(ISNUMBER(J24),MIN(J24/50,1),0))/MAX(1,COUNT(E24:H24,J24))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L24" s="18" t="str">
-        <f>IF(K24="","",IF(K24&gt;=0.7,5,IF(K24&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M24" s="2"/>
@@ -5329,11 +5330,11 @@
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="9" t="str">
-        <f>IF(COUNT(E25:J25)&lt;2,"",MIN(1,(IF(ISNUMBER(E25),MIN(E25/2,1),0)+IF(ISNUMBER(F25),F25,0)+IF(ISNUMBER(G25),G25/100,0)+IF(ISNUMBER(H25),MIN(H25/10,1),0)+IF(ISNUMBER(J25),MIN(J25/50,1),0))/MAX(1,COUNT(E25:H25,J25))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L25" s="18" t="str">
-        <f>IF(K25="","",IF(K25&gt;=0.7,5,IF(K25&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M25" s="2"/>
@@ -5350,11 +5351,11 @@
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="K26" s="9" t="str">
-        <f>IF(COUNT(E26:J26)&lt;2,"",MIN(1,(IF(ISNUMBER(E26),MIN(E26/2,1),0)+IF(ISNUMBER(F26),F26,0)+IF(ISNUMBER(G26),G26/100,0)+IF(ISNUMBER(H26),MIN(H26/10,1),0)+IF(ISNUMBER(J26),MIN(J26/50,1),0))/MAX(1,COUNT(E26:H26,J26))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L26" s="18" t="str">
-        <f>IF(K26="","",IF(K26&gt;=0.7,5,IF(K26&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M26" s="2"/>
@@ -5371,11 +5372,11 @@
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="9" t="str">
-        <f>IF(COUNT(E27:J27)&lt;2,"",MIN(1,(IF(ISNUMBER(E27),MIN(E27/2,1),0)+IF(ISNUMBER(F27),F27,0)+IF(ISNUMBER(G27),G27/100,0)+IF(ISNUMBER(H27),MIN(H27/10,1),0)+IF(ISNUMBER(J27),MIN(J27/50,1),0))/MAX(1,COUNT(E27:H27,J27))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L27" s="18" t="str">
-        <f>IF(K27="","",IF(K27&gt;=0.7,5,IF(K27&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M27" s="2"/>
@@ -5392,11 +5393,11 @@
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="9" t="str">
-        <f>IF(COUNT(E28:J28)&lt;2,"",MIN(1,(IF(ISNUMBER(E28),MIN(E28/2,1),0)+IF(ISNUMBER(F28),F28,0)+IF(ISNUMBER(G28),G28/100,0)+IF(ISNUMBER(H28),MIN(H28/10,1),0)+IF(ISNUMBER(J28),MIN(J28/50,1),0))/MAX(1,COUNT(E28:H28,J28))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L28" s="18" t="str">
-        <f>IF(K28="","",IF(K28&gt;=0.7,5,IF(K28&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M28" s="2"/>
@@ -5413,11 +5414,11 @@
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="K29" s="9" t="str">
-        <f>IF(COUNT(E29:J29)&lt;2,"",MIN(1,(IF(ISNUMBER(E29),MIN(E29/2,1),0)+IF(ISNUMBER(F29),F29,0)+IF(ISNUMBER(G29),G29/100,0)+IF(ISNUMBER(H29),MIN(H29/10,1),0)+IF(ISNUMBER(J29),MIN(J29/50,1),0))/MAX(1,COUNT(E29:H29,J29))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L29" s="18" t="str">
-        <f>IF(K29="","",IF(K29&gt;=0.7,5,IF(K29&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M29" s="2"/>
@@ -5434,11 +5435,11 @@
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="9" t="str">
-        <f>IF(COUNT(E30:J30)&lt;2,"",MIN(1,(IF(ISNUMBER(E30),MIN(E30/2,1),0)+IF(ISNUMBER(F30),F30,0)+IF(ISNUMBER(G30),G30/100,0)+IF(ISNUMBER(H30),MIN(H30/10,1),0)+IF(ISNUMBER(J30),MIN(J30/50,1),0))/MAX(1,COUNT(E30:H30,J30))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L30" s="18" t="str">
-        <f>IF(K30="","",IF(K30&gt;=0.7,5,IF(K30&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M30" s="2"/>
@@ -5455,11 +5456,11 @@
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="9" t="str">
-        <f>IF(COUNT(E31:J31)&lt;2,"",MIN(1,(IF(ISNUMBER(E31),MIN(E31/2,1),0)+IF(ISNUMBER(F31),F31,0)+IF(ISNUMBER(G31),G31/100,0)+IF(ISNUMBER(H31),MIN(H31/10,1),0)+IF(ISNUMBER(J31),MIN(J31/50,1),0))/MAX(1,COUNT(E31:H31,J31))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L31" s="18" t="str">
-        <f>IF(K31="","",IF(K31&gt;=0.7,5,IF(K31&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M31" s="2"/>
@@ -5476,11 +5477,11 @@
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="9" t="str">
-        <f>IF(COUNT(E32:J32)&lt;2,"",MIN(1,(IF(ISNUMBER(E32),MIN(E32/2,1),0)+IF(ISNUMBER(F32),F32,0)+IF(ISNUMBER(G32),G32/100,0)+IF(ISNUMBER(H32),MIN(H32/10,1),0)+IF(ISNUMBER(J32),MIN(J32/50,1),0))/MAX(1,COUNT(E32:H32,J32))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L32" s="18" t="str">
-        <f>IF(K32="","",IF(K32&gt;=0.7,5,IF(K32&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M32" s="2"/>
@@ -5497,11 +5498,11 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="9" t="str">
-        <f>IF(COUNT(E33:J33)&lt;2,"",MIN(1,(IF(ISNUMBER(E33),MIN(E33/2,1),0)+IF(ISNUMBER(F33),F33,0)+IF(ISNUMBER(G33),G33/100,0)+IF(ISNUMBER(H33),MIN(H33/10,1),0)+IF(ISNUMBER(J33),MIN(J33/50,1),0))/MAX(1,COUNT(E33:H33,J33))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L33" s="18" t="str">
-        <f>IF(K33="","",IF(K33&gt;=0.7,5,IF(K33&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M33" s="2"/>
@@ -5529,8 +5530,8 @@
         <v>нет данных</v>
       </c>
       <c r="C37" t="str">
-        <f>IF(ISNUMBER(B37),IF(B37&gt;=0.7,"высокое",IF(B37&gt;=0.4,"среднее","низкое")),"ДОСНЯТЬ")</f>
-        <v>ДОСНЯТЬ</v>
+        <f>IF(ISNUMBER(B37),IF(B37&gt;=0.7,"высокое",IF(B37&gt;=0.4,"среднее","низкое")),"нет данных")</f>
+        <v>нет данных</v>
       </c>
       <c r="D37" t="s">
         <v>189</v>
@@ -5545,8 +5546,8 @@
         <v>нет данных</v>
       </c>
       <c r="C38" t="str">
-        <f>IF(ISNUMBER(B38),IF(B38&gt;=0.5,"высокая доля",IF(B38&gt;=0.25,"средняя доля","низкая доля")),"ДОСНЯТЬ")</f>
-        <v>ДОСНЯТЬ</v>
+        <f>IF(ISNUMBER(B38),IF(B38&gt;=0.5,"высокая доля",IF(B38&gt;=0.25,"средняя доля","низкая доля")),"нет данных")</f>
+        <v>нет данных</v>
       </c>
       <c r="D38" t="s">
         <v>191</v>
@@ -5557,7 +5558,7 @@
         <v>192</v>
       </c>
       <c r="D39" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -5604,40 +5605,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="16.05" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
     </row>
     <row r="3" spans="1:14" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -5698,20 +5699,20 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="9" t="str">
-        <f>IF(COUNT(B4:K4)=0,"",MIN(1,(IF(COUNT(B4,D4,F4,H4)&gt;0,AVERAGE(B4,D4,F4,H4)/5,0)+IF(COUNT(C4,E4,G4,I4)&gt;0,MIN(SUM(C4,E4,G4,I4)/300,1),0)+IF(ISNUMBER(J4),MIN(J4/30,1),0)+IF(ISNUMBER(K4),MIN(K4/10,1),0))/MAX(1,(COUNT(B4,D4,F4,H4)&gt;0)+(COUNT(C4,E4,G4,I4)&gt;0)+ISNUMBER(J4)+ISNUMBER(K4))))</f>
+        <f t="shared" ref="L4:L33" si="0">IF(COUNT(B4:K4)=0,"",MIN(1,(IF(COUNT(B4,D4,F4,H4)&gt;0,AVERAGE(B4,D4,F4,H4)/5,0)+IF(COUNT(C4,E4,G4,I4)&gt;0,MIN(SUM(C4,E4,G4,I4)/300,1),0)+IF(ISNUMBER(J4),MIN(J4/30,1),0)+IF(ISNUMBER(K4),MIN(K4/10,1),0))/MAX(1,(COUNT(B4,D4,F4,H4)&gt;0)+(COUNT(C4,E4,G4,I4)&gt;0)+ISNUMBER(J4)+ISNUMBER(K4))))</f>
         <v/>
       </c>
       <c r="M4" s="18" t="str">
-        <f>IF(L4="","",IF(L4&gt;=0.7,5,IF(L4&gt;=0.4,3,1)))</f>
+        <f t="shared" ref="M4:M33" si="1">IF(L4="","",IF(L4&gt;=0.7,5,IF(L4&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N4" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27">
       <c r="A5" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="10">
@@ -5728,20 +5729,20 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="9">
-        <f>IF(COUNT(B5:K5)=0,"",MIN(1,(IF(COUNT(B5,D5,F5,H5)&gt;0,AVERAGE(B5,D5,F5,H5)/5,0)+IF(COUNT(C5,E5,G5,I5)&gt;0,MIN(SUM(C5,E5,G5,I5)/300,1),0)+IF(ISNUMBER(J5),MIN(J5/30,1),0)+IF(ISNUMBER(K5),MIN(K5/10,1),0))/MAX(1,(COUNT(B5,D5,F5,H5)&gt;0)+(COUNT(C5,E5,G5,I5)&gt;0)+ISNUMBER(J5)+ISNUMBER(K5))))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M5" s="18">
-        <f>IF(L5="","",IF(L5&gt;=0.7,5,IF(L5&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B6" s="19">
         <v>4.9000000000000004</v>
@@ -5758,20 +5759,20 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="9">
-        <f>IF(COUNT(B6:K6)=0,"",MIN(1,(IF(COUNT(B6,D6,F6,H6)&gt;0,AVERAGE(B6,D6,F6,H6)/5,0)+IF(COUNT(C6,E6,G6,I6)&gt;0,MIN(SUM(C6,E6,G6,I6)/300,1),0)+IF(ISNUMBER(J6),MIN(J6/30,1),0)+IF(ISNUMBER(K6),MIN(K6/10,1),0))/MAX(1,(COUNT(B6,D6,F6,H6)&gt;0)+(COUNT(C6,E6,G6,I6)&gt;0)+ISNUMBER(J6)+ISNUMBER(K6))))</f>
+        <f t="shared" si="0"/>
         <v>0.53</v>
       </c>
       <c r="M6" s="18">
-        <f>IF(L6="","",IF(L6&gt;=0.7,5,IF(L6&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="27">
       <c r="A7" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="10"/>
@@ -5784,20 +5785,20 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="9" t="str">
-        <f>IF(COUNT(B7:K7)=0,"",MIN(1,(IF(COUNT(B7,D7,F7,H7)&gt;0,AVERAGE(B7,D7,F7,H7)/5,0)+IF(COUNT(C7,E7,G7,I7)&gt;0,MIN(SUM(C7,E7,G7,I7)/300,1),0)+IF(ISNUMBER(J7),MIN(J7/30,1),0)+IF(ISNUMBER(K7),MIN(K7/10,1),0))/MAX(1,(COUNT(B7,D7,F7,H7)&gt;0)+(COUNT(C7,E7,G7,I7)&gt;0)+ISNUMBER(J7)+ISNUMBER(K7))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M7" s="18" t="str">
-        <f>IF(L7="","",IF(L7&gt;=0.7,5,IF(L7&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N7" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="54">
       <c r="A8" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="10"/>
@@ -5810,20 +5811,20 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="9" t="str">
-        <f>IF(COUNT(B8:K8)=0,"",MIN(1,(IF(COUNT(B8,D8,F8,H8)&gt;0,AVERAGE(B8,D8,F8,H8)/5,0)+IF(COUNT(C8,E8,G8,I8)&gt;0,MIN(SUM(C8,E8,G8,I8)/300,1),0)+IF(ISNUMBER(J8),MIN(J8/30,1),0)+IF(ISNUMBER(K8),MIN(K8/10,1),0))/MAX(1,(COUNT(B8,D8,F8,H8)&gt;0)+(COUNT(C8,E8,G8,I8)&gt;0)+ISNUMBER(J8)+ISNUMBER(K8))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M8" s="18" t="str">
-        <f>IF(L8="","",IF(L8&gt;=0.7,5,IF(L8&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N8" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B9" s="19">
         <v>4</v>
@@ -5840,20 +5841,20 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="9">
-        <f>IF(COUNT(B9:K9)=0,"",MIN(1,(IF(COUNT(B9,D9,F9,H9)&gt;0,AVERAGE(B9,D9,F9,H9)/5,0)+IF(COUNT(C9,E9,G9,I9)&gt;0,MIN(SUM(C9,E9,G9,I9)/300,1),0)+IF(ISNUMBER(J9),MIN(J9/30,1),0)+IF(ISNUMBER(K9),MIN(K9/10,1),0))/MAX(1,(COUNT(B9,D9,F9,H9)&gt;0)+(COUNT(C9,E9,G9,I9)&gt;0)+ISNUMBER(J9)+ISNUMBER(K9))))</f>
+        <f t="shared" si="0"/>
         <v>0.40166666666666667</v>
       </c>
       <c r="M9" s="18">
-        <f>IF(L9="","",IF(L9&gt;=0.7,5,IF(L9&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B10" s="19">
         <v>4.5</v>
@@ -5870,20 +5871,20 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="9">
-        <f>IF(COUNT(B10:K10)=0,"",MIN(1,(IF(COUNT(B10,D10,F10,H10)&gt;0,AVERAGE(B10,D10,F10,H10)/5,0)+IF(COUNT(C10,E10,G10,I10)&gt;0,MIN(SUM(C10,E10,G10,I10)/300,1),0)+IF(ISNUMBER(J10),MIN(J10/30,1),0)+IF(ISNUMBER(K10),MIN(K10/10,1),0))/MAX(1,(COUNT(B10,D10,F10,H10)&gt;0)+(COUNT(C10,E10,G10,I10)&gt;0)+ISNUMBER(J10)+ISNUMBER(K10))))</f>
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="M10" s="18">
-        <f>IF(L10="","",IF(L10&gt;=0.7,5,IF(L10&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B11" s="19">
         <v>4.5</v>
@@ -5900,20 +5901,20 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="9">
-        <f>IF(COUNT(B11:K11)=0,"",MIN(1,(IF(COUNT(B11,D11,F11,H11)&gt;0,AVERAGE(B11,D11,F11,H11)/5,0)+IF(COUNT(C11,E11,G11,I11)&gt;0,MIN(SUM(C11,E11,G11,I11)/300,1),0)+IF(ISNUMBER(J11),MIN(J11/30,1),0)+IF(ISNUMBER(K11),MIN(K11/10,1),0))/MAX(1,(COUNT(B11,D11,F11,H11)&gt;0)+(COUNT(C11,E11,G11,I11)&gt;0)+ISNUMBER(J11)+ISNUMBER(K11))))</f>
+        <f t="shared" si="0"/>
         <v>0.45166666666666666</v>
       </c>
       <c r="M11" s="18">
-        <f>IF(L11="","",IF(L11&gt;=0.7,5,IF(L11&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B12" s="19">
         <v>4.5999999999999996</v>
@@ -5930,20 +5931,20 @@
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="9">
-        <f>IF(COUNT(B12:K12)=0,"",MIN(1,(IF(COUNT(B12,D12,F12,H12)&gt;0,AVERAGE(B12,D12,F12,H12)/5,0)+IF(COUNT(C12,E12,G12,I12)&gt;0,MIN(SUM(C12,E12,G12,I12)/300,1),0)+IF(ISNUMBER(J12),MIN(J12/30,1),0)+IF(ISNUMBER(K12),MIN(K12/10,1),0))/MAX(1,(COUNT(B12,D12,F12,H12)&gt;0)+(COUNT(C12,E12,G12,I12)&gt;0)+ISNUMBER(J12)+ISNUMBER(K12))))</f>
+        <f t="shared" si="0"/>
         <v>0.96</v>
       </c>
       <c r="M12" s="18">
-        <f>IF(L12="","",IF(L12&gt;=0.7,5,IF(L12&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B13" s="19">
         <v>4.5</v>
@@ -5960,20 +5961,20 @@
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="9">
-        <f>IF(COUNT(B13:K13)=0,"",MIN(1,(IF(COUNT(B13,D13,F13,H13)&gt;0,AVERAGE(B13,D13,F13,H13)/5,0)+IF(COUNT(C13,E13,G13,I13)&gt;0,MIN(SUM(C13,E13,G13,I13)/300,1),0)+IF(ISNUMBER(J13),MIN(J13/30,1),0)+IF(ISNUMBER(K13),MIN(K13/10,1),0))/MAX(1,(COUNT(B13,D13,F13,H13)&gt;0)+(COUNT(C13,E13,G13,I13)&gt;0)+ISNUMBER(J13)+ISNUMBER(K13))))</f>
+        <f t="shared" si="0"/>
         <v>0.45666666666666667</v>
       </c>
       <c r="M13" s="18">
-        <f>IF(L13="","",IF(L13&gt;=0.7,5,IF(L13&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="10">
@@ -5988,20 +5989,20 @@
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="9">
-        <f>IF(COUNT(B14:K14)=0,"",MIN(1,(IF(COUNT(B14,D14,F14,H14)&gt;0,AVERAGE(B14,D14,F14,H14)/5,0)+IF(COUNT(C14,E14,G14,I14)&gt;0,MIN(SUM(C14,E14,G14,I14)/300,1),0)+IF(ISNUMBER(J14),MIN(J14/30,1),0)+IF(ISNUMBER(K14),MIN(K14/10,1),0))/MAX(1,(COUNT(B14,D14,F14,H14)&gt;0)+(COUNT(C14,E14,G14,I14)&gt;0)+ISNUMBER(J14)+ISNUMBER(K14))))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M14" s="18">
-        <f>IF(L14="","",IF(L14&gt;=0.7,5,IF(L14&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="27">
       <c r="A15" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B15" s="19">
         <v>4.7</v>
@@ -6018,15 +6019,15 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="9">
-        <f>IF(COUNT(B15:K15)=0,"",MIN(1,(IF(COUNT(B15,D15,F15,H15)&gt;0,AVERAGE(B15,D15,F15,H15)/5,0)+IF(COUNT(C15,E15,G15,I15)&gt;0,MIN(SUM(C15,E15,G15,I15)/300,1),0)+IF(ISNUMBER(J15),MIN(J15/30,1),0)+IF(ISNUMBER(K15),MIN(K15/10,1),0))/MAX(1,(COUNT(B15,D15,F15,H15)&gt;0)+(COUNT(C15,E15,G15,I15)&gt;0)+ISNUMBER(J15)+ISNUMBER(K15))))</f>
+        <f t="shared" si="0"/>
         <v>0.50166666666666671</v>
       </c>
       <c r="M15" s="18">
-        <f>IF(L15="","",IF(L15&gt;=0.7,5,IF(L15&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -6042,11 +6043,11 @@
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="9" t="str">
-        <f>IF(COUNT(B16:K16)=0,"",MIN(1,(IF(COUNT(B16,D16,F16,H16)&gt;0,AVERAGE(B16,D16,F16,H16)/5,0)+IF(COUNT(C16,E16,G16,I16)&gt;0,MIN(SUM(C16,E16,G16,I16)/300,1),0)+IF(ISNUMBER(J16),MIN(J16/30,1),0)+IF(ISNUMBER(K16),MIN(K16/10,1),0))/MAX(1,(COUNT(B16,D16,F16,H16)&gt;0)+(COUNT(C16,E16,G16,I16)&gt;0)+ISNUMBER(J16)+ISNUMBER(K16))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M16" s="18" t="str">
-        <f>IF(L16="","",IF(L16&gt;=0.7,5,IF(L16&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N16" s="2"/>
@@ -6064,11 +6065,11 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="9" t="str">
-        <f>IF(COUNT(B17:K17)=0,"",MIN(1,(IF(COUNT(B17,D17,F17,H17)&gt;0,AVERAGE(B17,D17,F17,H17)/5,0)+IF(COUNT(C17,E17,G17,I17)&gt;0,MIN(SUM(C17,E17,G17,I17)/300,1),0)+IF(ISNUMBER(J17),MIN(J17/30,1),0)+IF(ISNUMBER(K17),MIN(K17/10,1),0))/MAX(1,(COUNT(B17,D17,F17,H17)&gt;0)+(COUNT(C17,E17,G17,I17)&gt;0)+ISNUMBER(J17)+ISNUMBER(K17))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M17" s="18" t="str">
-        <f>IF(L17="","",IF(L17&gt;=0.7,5,IF(L17&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N17" s="2"/>
@@ -6086,11 +6087,11 @@
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="9" t="str">
-        <f>IF(COUNT(B18:K18)=0,"",MIN(1,(IF(COUNT(B18,D18,F18,H18)&gt;0,AVERAGE(B18,D18,F18,H18)/5,0)+IF(COUNT(C18,E18,G18,I18)&gt;0,MIN(SUM(C18,E18,G18,I18)/300,1),0)+IF(ISNUMBER(J18),MIN(J18/30,1),0)+IF(ISNUMBER(K18),MIN(K18/10,1),0))/MAX(1,(COUNT(B18,D18,F18,H18)&gt;0)+(COUNT(C18,E18,G18,I18)&gt;0)+ISNUMBER(J18)+ISNUMBER(K18))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M18" s="18" t="str">
-        <f>IF(L18="","",IF(L18&gt;=0.7,5,IF(L18&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N18" s="2"/>
@@ -6108,11 +6109,11 @@
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="9" t="str">
-        <f>IF(COUNT(B19:K19)=0,"",MIN(1,(IF(COUNT(B19,D19,F19,H19)&gt;0,AVERAGE(B19,D19,F19,H19)/5,0)+IF(COUNT(C19,E19,G19,I19)&gt;0,MIN(SUM(C19,E19,G19,I19)/300,1),0)+IF(ISNUMBER(J19),MIN(J19/30,1),0)+IF(ISNUMBER(K19),MIN(K19/10,1),0))/MAX(1,(COUNT(B19,D19,F19,H19)&gt;0)+(COUNT(C19,E19,G19,I19)&gt;0)+ISNUMBER(J19)+ISNUMBER(K19))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M19" s="18" t="str">
-        <f>IF(L19="","",IF(L19&gt;=0.7,5,IF(L19&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N19" s="2"/>
@@ -6130,11 +6131,11 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="9" t="str">
-        <f>IF(COUNT(B20:K20)=0,"",MIN(1,(IF(COUNT(B20,D20,F20,H20)&gt;0,AVERAGE(B20,D20,F20,H20)/5,0)+IF(COUNT(C20,E20,G20,I20)&gt;0,MIN(SUM(C20,E20,G20,I20)/300,1),0)+IF(ISNUMBER(J20),MIN(J20/30,1),0)+IF(ISNUMBER(K20),MIN(K20/10,1),0))/MAX(1,(COUNT(B20,D20,F20,H20)&gt;0)+(COUNT(C20,E20,G20,I20)&gt;0)+ISNUMBER(J20)+ISNUMBER(K20))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M20" s="18" t="str">
-        <f>IF(L20="","",IF(L20&gt;=0.7,5,IF(L20&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N20" s="2"/>
@@ -6152,11 +6153,11 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="9" t="str">
-        <f>IF(COUNT(B21:K21)=0,"",MIN(1,(IF(COUNT(B21,D21,F21,H21)&gt;0,AVERAGE(B21,D21,F21,H21)/5,0)+IF(COUNT(C21,E21,G21,I21)&gt;0,MIN(SUM(C21,E21,G21,I21)/300,1),0)+IF(ISNUMBER(J21),MIN(J21/30,1),0)+IF(ISNUMBER(K21),MIN(K21/10,1),0))/MAX(1,(COUNT(B21,D21,F21,H21)&gt;0)+(COUNT(C21,E21,G21,I21)&gt;0)+ISNUMBER(J21)+ISNUMBER(K21))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M21" s="18" t="str">
-        <f>IF(L21="","",IF(L21&gt;=0.7,5,IF(L21&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N21" s="2"/>
@@ -6174,11 +6175,11 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="9" t="str">
-        <f>IF(COUNT(B22:K22)=0,"",MIN(1,(IF(COUNT(B22,D22,F22,H22)&gt;0,AVERAGE(B22,D22,F22,H22)/5,0)+IF(COUNT(C22,E22,G22,I22)&gt;0,MIN(SUM(C22,E22,G22,I22)/300,1),0)+IF(ISNUMBER(J22),MIN(J22/30,1),0)+IF(ISNUMBER(K22),MIN(K22/10,1),0))/MAX(1,(COUNT(B22,D22,F22,H22)&gt;0)+(COUNT(C22,E22,G22,I22)&gt;0)+ISNUMBER(J22)+ISNUMBER(K22))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M22" s="18" t="str">
-        <f>IF(L22="","",IF(L22&gt;=0.7,5,IF(L22&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N22" s="2"/>
@@ -6196,11 +6197,11 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="9" t="str">
-        <f>IF(COUNT(B23:K23)=0,"",MIN(1,(IF(COUNT(B23,D23,F23,H23)&gt;0,AVERAGE(B23,D23,F23,H23)/5,0)+IF(COUNT(C23,E23,G23,I23)&gt;0,MIN(SUM(C23,E23,G23,I23)/300,1),0)+IF(ISNUMBER(J23),MIN(J23/30,1),0)+IF(ISNUMBER(K23),MIN(K23/10,1),0))/MAX(1,(COUNT(B23,D23,F23,H23)&gt;0)+(COUNT(C23,E23,G23,I23)&gt;0)+ISNUMBER(J23)+ISNUMBER(K23))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M23" s="18" t="str">
-        <f>IF(L23="","",IF(L23&gt;=0.7,5,IF(L23&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N23" s="2"/>
@@ -6218,11 +6219,11 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="9" t="str">
-        <f>IF(COUNT(B24:K24)=0,"",MIN(1,(IF(COUNT(B24,D24,F24,H24)&gt;0,AVERAGE(B24,D24,F24,H24)/5,0)+IF(COUNT(C24,E24,G24,I24)&gt;0,MIN(SUM(C24,E24,G24,I24)/300,1),0)+IF(ISNUMBER(J24),MIN(J24/30,1),0)+IF(ISNUMBER(K24),MIN(K24/10,1),0))/MAX(1,(COUNT(B24,D24,F24,H24)&gt;0)+(COUNT(C24,E24,G24,I24)&gt;0)+ISNUMBER(J24)+ISNUMBER(K24))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M24" s="18" t="str">
-        <f>IF(L24="","",IF(L24&gt;=0.7,5,IF(L24&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N24" s="2"/>
@@ -6240,11 +6241,11 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="9" t="str">
-        <f>IF(COUNT(B25:K25)=0,"",MIN(1,(IF(COUNT(B25,D25,F25,H25)&gt;0,AVERAGE(B25,D25,F25,H25)/5,0)+IF(COUNT(C25,E25,G25,I25)&gt;0,MIN(SUM(C25,E25,G25,I25)/300,1),0)+IF(ISNUMBER(J25),MIN(J25/30,1),0)+IF(ISNUMBER(K25),MIN(K25/10,1),0))/MAX(1,(COUNT(B25,D25,F25,H25)&gt;0)+(COUNT(C25,E25,G25,I25)&gt;0)+ISNUMBER(J25)+ISNUMBER(K25))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M25" s="18" t="str">
-        <f>IF(L25="","",IF(L25&gt;=0.7,5,IF(L25&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N25" s="2"/>
@@ -6262,11 +6263,11 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="9" t="str">
-        <f>IF(COUNT(B26:K26)=0,"",MIN(1,(IF(COUNT(B26,D26,F26,H26)&gt;0,AVERAGE(B26,D26,F26,H26)/5,0)+IF(COUNT(C26,E26,G26,I26)&gt;0,MIN(SUM(C26,E26,G26,I26)/300,1),0)+IF(ISNUMBER(J26),MIN(J26/30,1),0)+IF(ISNUMBER(K26),MIN(K26/10,1),0))/MAX(1,(COUNT(B26,D26,F26,H26)&gt;0)+(COUNT(C26,E26,G26,I26)&gt;0)+ISNUMBER(J26)+ISNUMBER(K26))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M26" s="18" t="str">
-        <f>IF(L26="","",IF(L26&gt;=0.7,5,IF(L26&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N26" s="2"/>
@@ -6284,11 +6285,11 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="9" t="str">
-        <f>IF(COUNT(B27:K27)=0,"",MIN(1,(IF(COUNT(B27,D27,F27,H27)&gt;0,AVERAGE(B27,D27,F27,H27)/5,0)+IF(COUNT(C27,E27,G27,I27)&gt;0,MIN(SUM(C27,E27,G27,I27)/300,1),0)+IF(ISNUMBER(J27),MIN(J27/30,1),0)+IF(ISNUMBER(K27),MIN(K27/10,1),0))/MAX(1,(COUNT(B27,D27,F27,H27)&gt;0)+(COUNT(C27,E27,G27,I27)&gt;0)+ISNUMBER(J27)+ISNUMBER(K27))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M27" s="18" t="str">
-        <f>IF(L27="","",IF(L27&gt;=0.7,5,IF(L27&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N27" s="2"/>
@@ -6306,11 +6307,11 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="9" t="str">
-        <f>IF(COUNT(B28:K28)=0,"",MIN(1,(IF(COUNT(B28,D28,F28,H28)&gt;0,AVERAGE(B28,D28,F28,H28)/5,0)+IF(COUNT(C28,E28,G28,I28)&gt;0,MIN(SUM(C28,E28,G28,I28)/300,1),0)+IF(ISNUMBER(J28),MIN(J28/30,1),0)+IF(ISNUMBER(K28),MIN(K28/10,1),0))/MAX(1,(COUNT(B28,D28,F28,H28)&gt;0)+(COUNT(C28,E28,G28,I28)&gt;0)+ISNUMBER(J28)+ISNUMBER(K28))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M28" s="18" t="str">
-        <f>IF(L28="","",IF(L28&gt;=0.7,5,IF(L28&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N28" s="2"/>
@@ -6328,11 +6329,11 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="9" t="str">
-        <f>IF(COUNT(B29:K29)=0,"",MIN(1,(IF(COUNT(B29,D29,F29,H29)&gt;0,AVERAGE(B29,D29,F29,H29)/5,0)+IF(COUNT(C29,E29,G29,I29)&gt;0,MIN(SUM(C29,E29,G29,I29)/300,1),0)+IF(ISNUMBER(J29),MIN(J29/30,1),0)+IF(ISNUMBER(K29),MIN(K29/10,1),0))/MAX(1,(COUNT(B29,D29,F29,H29)&gt;0)+(COUNT(C29,E29,G29,I29)&gt;0)+ISNUMBER(J29)+ISNUMBER(K29))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M29" s="18" t="str">
-        <f>IF(L29="","",IF(L29&gt;=0.7,5,IF(L29&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N29" s="2"/>
@@ -6350,11 +6351,11 @@
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="9" t="str">
-        <f>IF(COUNT(B30:K30)=0,"",MIN(1,(IF(COUNT(B30,D30,F30,H30)&gt;0,AVERAGE(B30,D30,F30,H30)/5,0)+IF(COUNT(C30,E30,G30,I30)&gt;0,MIN(SUM(C30,E30,G30,I30)/300,1),0)+IF(ISNUMBER(J30),MIN(J30/30,1),0)+IF(ISNUMBER(K30),MIN(K30/10,1),0))/MAX(1,(COUNT(B30,D30,F30,H30)&gt;0)+(COUNT(C30,E30,G30,I30)&gt;0)+ISNUMBER(J30)+ISNUMBER(K30))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M30" s="18" t="str">
-        <f>IF(L30="","",IF(L30&gt;=0.7,5,IF(L30&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N30" s="2"/>
@@ -6372,11 +6373,11 @@
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="9" t="str">
-        <f>IF(COUNT(B31:K31)=0,"",MIN(1,(IF(COUNT(B31,D31,F31,H31)&gt;0,AVERAGE(B31,D31,F31,H31)/5,0)+IF(COUNT(C31,E31,G31,I31)&gt;0,MIN(SUM(C31,E31,G31,I31)/300,1),0)+IF(ISNUMBER(J31),MIN(J31/30,1),0)+IF(ISNUMBER(K31),MIN(K31/10,1),0))/MAX(1,(COUNT(B31,D31,F31,H31)&gt;0)+(COUNT(C31,E31,G31,I31)&gt;0)+ISNUMBER(J31)+ISNUMBER(K31))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M31" s="18" t="str">
-        <f>IF(L31="","",IF(L31&gt;=0.7,5,IF(L31&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N31" s="2"/>
@@ -6394,11 +6395,11 @@
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="9" t="str">
-        <f>IF(COUNT(B32:K32)=0,"",MIN(1,(IF(COUNT(B32,D32,F32,H32)&gt;0,AVERAGE(B32,D32,F32,H32)/5,0)+IF(COUNT(C32,E32,G32,I32)&gt;0,MIN(SUM(C32,E32,G32,I32)/300,1),0)+IF(ISNUMBER(J32),MIN(J32/30,1),0)+IF(ISNUMBER(K32),MIN(K32/10,1),0))/MAX(1,(COUNT(B32,D32,F32,H32)&gt;0)+(COUNT(C32,E32,G32,I32)&gt;0)+ISNUMBER(J32)+ISNUMBER(K32))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M32" s="18" t="str">
-        <f>IF(L32="","",IF(L32&gt;=0.7,5,IF(L32&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N32" s="2"/>
@@ -6416,11 +6417,11 @@
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="9" t="str">
-        <f>IF(COUNT(B33:K33)=0,"",MIN(1,(IF(COUNT(B33,D33,F33,H33)&gt;0,AVERAGE(B33,D33,F33,H33)/5,0)+IF(COUNT(C33,E33,G33,I33)&gt;0,MIN(SUM(C33,E33,G33,I33)/300,1),0)+IF(ISNUMBER(J33),MIN(J33/30,1),0)+IF(ISNUMBER(K33),MIN(K33/10,1),0))/MAX(1,(COUNT(B33,D33,F33,H33)&gt;0)+(COUNT(C33,E33,G33,I33)&gt;0)+ISNUMBER(J33)+ISNUMBER(K33))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M33" s="18" t="str">
-        <f>IF(L33="","",IF(L33&gt;=0.7,5,IF(L33&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N33" s="2"/>
@@ -6468,7 +6469,7 @@
         <v>низкий барьер</v>
       </c>
       <c r="D38" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -6513,38 +6514,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
     </row>
     <row r="2" spans="1:13" ht="16.05" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
     </row>
     <row r="3" spans="1:13" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -6605,20 +6606,20 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="9">
-        <f>IF(COUNTA(B4:J4)=0,"",MIN(1,(IF(ISNUMBER(B4),MIN(B4/500000,1),0)+IF(ISNUMBER(C4),MIN(C4/60,1),0)+IF(ISNUMBER(D4),D4/5,0)+IF(ISNUMBER(E4),E4/5,0)+IF(F4="да",1,0)+IF(G4="да",1,0)+IF(ISNUMBER(H4),MIN(H4/50,1),0)+IF(ISNUMBER(I4),MIN(I4/6,1),0)+IF(ISNUMBER(J4),IF(J4&gt;0,1,0),0))/MAX(1,ISNUMBER(B4)+ISNUMBER(C4)+ISNUMBER(D4)+ISNUMBER(E4)+(F4&lt;&gt;"")+(G4&lt;&gt;"")+ISNUMBER(H4)+ISNUMBER(I4)+ISNUMBER(J4))))</f>
+        <f t="shared" ref="K4:K33" si="0">IF(COUNTA(B4:J4)=0,"",MIN(1,(IF(ISNUMBER(B4),MIN(B4/500000,1),0)+IF(ISNUMBER(C4),MIN(C4/60,1),0)+IF(ISNUMBER(D4),D4/5,0)+IF(ISNUMBER(E4),E4/5,0)+IF(F4="да",1,0)+IF(G4="да",1,0)+IF(ISNUMBER(H4),MIN(H4/50,1),0)+IF(ISNUMBER(I4),MIN(I4/6,1),0)+IF(ISNUMBER(J4),IF(J4&gt;0,1,0),0))/MAX(1,ISNUMBER(B4)+ISNUMBER(C4)+ISNUMBER(D4)+ISNUMBER(E4)+(F4&lt;&gt;"")+(G4&lt;&gt;"")+ISNUMBER(H4)+ISNUMBER(I4)+ISNUMBER(J4))))</f>
         <v>1</v>
       </c>
       <c r="L4" s="18">
-        <f>IF(K4="","",IF(K4&gt;=0.7,5,IF(K4&gt;=0.4,3,1)))</f>
+        <f t="shared" ref="L4:L33" si="1">IF(K4="","",IF(K4&gt;=0.7,5,IF(K4&gt;=0.4,3,1)))</f>
         <v>5</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54">
       <c r="A5" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="17"/>
@@ -6634,20 +6635,20 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="9">
-        <f>IF(COUNTA(B5:J5)=0,"",MIN(1,(IF(ISNUMBER(B5),MIN(B5/500000,1),0)+IF(ISNUMBER(C5),MIN(C5/60,1),0)+IF(ISNUMBER(D5),D5/5,0)+IF(ISNUMBER(E5),E5/5,0)+IF(F5="да",1,0)+IF(G5="да",1,0)+IF(ISNUMBER(H5),MIN(H5/50,1),0)+IF(ISNUMBER(I5),MIN(I5/6,1),0)+IF(ISNUMBER(J5),IF(J5&gt;0,1,0),0))/MAX(1,ISNUMBER(B5)+ISNUMBER(C5)+ISNUMBER(D5)+ISNUMBER(E5)+(F5&lt;&gt;"")+(G5&lt;&gt;"")+ISNUMBER(H5)+ISNUMBER(I5)+ISNUMBER(J5))))</f>
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="L5" s="18">
-        <f>IF(K5="","",IF(K5&gt;=0.7,5,IF(K5&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="54">
       <c r="A6" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="17"/>
@@ -6663,20 +6664,20 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="9">
-        <f>IF(COUNTA(B6:J6)=0,"",MIN(1,(IF(ISNUMBER(B6),MIN(B6/500000,1),0)+IF(ISNUMBER(C6),MIN(C6/60,1),0)+IF(ISNUMBER(D6),D6/5,0)+IF(ISNUMBER(E6),E6/5,0)+IF(F6="да",1,0)+IF(G6="да",1,0)+IF(ISNUMBER(H6),MIN(H6/50,1),0)+IF(ISNUMBER(I6),MIN(I6/6,1),0)+IF(ISNUMBER(J6),IF(J6&gt;0,1,0),0))/MAX(1,ISNUMBER(B6)+ISNUMBER(C6)+ISNUMBER(D6)+ISNUMBER(E6)+(F6&lt;&gt;"")+(G6&lt;&gt;"")+ISNUMBER(H6)+ISNUMBER(I6)+ISNUMBER(J6))))</f>
+        <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
       <c r="L6" s="18">
-        <f>IF(K6="","",IF(K6&gt;=0.7,5,IF(K6&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54">
       <c r="A7" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="17"/>
@@ -6692,20 +6693,20 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="9">
-        <f>IF(COUNTA(B7:J7)=0,"",MIN(1,(IF(ISNUMBER(B7),MIN(B7/500000,1),0)+IF(ISNUMBER(C7),MIN(C7/60,1),0)+IF(ISNUMBER(D7),D7/5,0)+IF(ISNUMBER(E7),E7/5,0)+IF(F7="да",1,0)+IF(G7="да",1,0)+IF(ISNUMBER(H7),MIN(H7/50,1),0)+IF(ISNUMBER(I7),MIN(I7/6,1),0)+IF(ISNUMBER(J7),IF(J7&gt;0,1,0),0))/MAX(1,ISNUMBER(B7)+ISNUMBER(C7)+ISNUMBER(D7)+ISNUMBER(E7)+(F7&lt;&gt;"")+(G7&lt;&gt;"")+ISNUMBER(H7)+ISNUMBER(I7)+ISNUMBER(J7))))</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="L7" s="18">
-        <f>IF(K7="","",IF(K7&gt;=0.7,5,IF(K7&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54">
       <c r="A8" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="17"/>
@@ -6721,20 +6722,20 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="9">
-        <f>IF(COUNTA(B8:J8)=0,"",MIN(1,(IF(ISNUMBER(B8),MIN(B8/500000,1),0)+IF(ISNUMBER(C8),MIN(C8/60,1),0)+IF(ISNUMBER(D8),D8/5,0)+IF(ISNUMBER(E8),E8/5,0)+IF(F8="да",1,0)+IF(G8="да",1,0)+IF(ISNUMBER(H8),MIN(H8/50,1),0)+IF(ISNUMBER(I8),MIN(I8/6,1),0)+IF(ISNUMBER(J8),IF(J8&gt;0,1,0),0))/MAX(1,ISNUMBER(B8)+ISNUMBER(C8)+ISNUMBER(D8)+ISNUMBER(E8)+(F8&lt;&gt;"")+(G8&lt;&gt;"")+ISNUMBER(H8)+ISNUMBER(I8)+ISNUMBER(J8))))</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="L8" s="18">
-        <f>IF(K8="","",IF(K8&gt;=0.7,5,IF(K8&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="54">
       <c r="A9" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="17"/>
@@ -6750,20 +6751,20 @@
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="9">
-        <f>IF(COUNTA(B9:J9)=0,"",MIN(1,(IF(ISNUMBER(B9),MIN(B9/500000,1),0)+IF(ISNUMBER(C9),MIN(C9/60,1),0)+IF(ISNUMBER(D9),D9/5,0)+IF(ISNUMBER(E9),E9/5,0)+IF(F9="да",1,0)+IF(G9="да",1,0)+IF(ISNUMBER(H9),MIN(H9/50,1),0)+IF(ISNUMBER(I9),MIN(I9/6,1),0)+IF(ISNUMBER(J9),IF(J9&gt;0,1,0),0))/MAX(1,ISNUMBER(B9)+ISNUMBER(C9)+ISNUMBER(D9)+ISNUMBER(E9)+(F9&lt;&gt;"")+(G9&lt;&gt;"")+ISNUMBER(H9)+ISNUMBER(I9)+ISNUMBER(J9))))</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="L9" s="18">
-        <f>IF(K9="","",IF(K9&gt;=0.7,5,IF(K9&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="54">
       <c r="A10" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="17"/>
@@ -6779,20 +6780,20 @@
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="9">
-        <f>IF(COUNTA(B10:J10)=0,"",MIN(1,(IF(ISNUMBER(B10),MIN(B10/500000,1),0)+IF(ISNUMBER(C10),MIN(C10/60,1),0)+IF(ISNUMBER(D10),D10/5,0)+IF(ISNUMBER(E10),E10/5,0)+IF(F10="да",1,0)+IF(G10="да",1,0)+IF(ISNUMBER(H10),MIN(H10/50,1),0)+IF(ISNUMBER(I10),MIN(I10/6,1),0)+IF(ISNUMBER(J10),IF(J10&gt;0,1,0),0))/MAX(1,ISNUMBER(B10)+ISNUMBER(C10)+ISNUMBER(D10)+ISNUMBER(E10)+(F10&lt;&gt;"")+(G10&lt;&gt;"")+ISNUMBER(H10)+ISNUMBER(I10)+ISNUMBER(J10))))</f>
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="L10" s="18">
-        <f>IF(K10="","",IF(K10&gt;=0.7,5,IF(K10&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="54">
       <c r="A11" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="17"/>
@@ -6808,20 +6809,20 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="9">
-        <f>IF(COUNTA(B11:J11)=0,"",MIN(1,(IF(ISNUMBER(B11),MIN(B11/500000,1),0)+IF(ISNUMBER(C11),MIN(C11/60,1),0)+IF(ISNUMBER(D11),D11/5,0)+IF(ISNUMBER(E11),E11/5,0)+IF(F11="да",1,0)+IF(G11="да",1,0)+IF(ISNUMBER(H11),MIN(H11/50,1),0)+IF(ISNUMBER(I11),MIN(I11/6,1),0)+IF(ISNUMBER(J11),IF(J11&gt;0,1,0),0))/MAX(1,ISNUMBER(B11)+ISNUMBER(C11)+ISNUMBER(D11)+ISNUMBER(E11)+(F11&lt;&gt;"")+(G11&lt;&gt;"")+ISNUMBER(H11)+ISNUMBER(I11)+ISNUMBER(J11))))</f>
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="L11" s="18">
-        <f>IF(K11="","",IF(K11&gt;=0.7,5,IF(K11&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54">
       <c r="A12" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="17"/>
@@ -6837,20 +6838,20 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="9">
-        <f>IF(COUNTA(B12:J12)=0,"",MIN(1,(IF(ISNUMBER(B12),MIN(B12/500000,1),0)+IF(ISNUMBER(C12),MIN(C12/60,1),0)+IF(ISNUMBER(D12),D12/5,0)+IF(ISNUMBER(E12),E12/5,0)+IF(F12="да",1,0)+IF(G12="да",1,0)+IF(ISNUMBER(H12),MIN(H12/50,1),0)+IF(ISNUMBER(I12),MIN(I12/6,1),0)+IF(ISNUMBER(J12),IF(J12&gt;0,1,0),0))/MAX(1,ISNUMBER(B12)+ISNUMBER(C12)+ISNUMBER(D12)+ISNUMBER(E12)+(F12&lt;&gt;"")+(G12&lt;&gt;"")+ISNUMBER(H12)+ISNUMBER(I12)+ISNUMBER(J12))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L12" s="18">
-        <f>IF(K12="","",IF(K12&gt;=0.7,5,IF(K12&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="54">
       <c r="A13" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="17"/>
@@ -6866,20 +6867,20 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="9">
-        <f>IF(COUNTA(B13:J13)=0,"",MIN(1,(IF(ISNUMBER(B13),MIN(B13/500000,1),0)+IF(ISNUMBER(C13),MIN(C13/60,1),0)+IF(ISNUMBER(D13),D13/5,0)+IF(ISNUMBER(E13),E13/5,0)+IF(F13="да",1,0)+IF(G13="да",1,0)+IF(ISNUMBER(H13),MIN(H13/50,1),0)+IF(ISNUMBER(I13),MIN(I13/6,1),0)+IF(ISNUMBER(J13),IF(J13&gt;0,1,0),0))/MAX(1,ISNUMBER(B13)+ISNUMBER(C13)+ISNUMBER(D13)+ISNUMBER(E13)+(F13&lt;&gt;"")+(G13&lt;&gt;"")+ISNUMBER(H13)+ISNUMBER(I13)+ISNUMBER(J13))))</f>
+        <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
       <c r="L13" s="18">
-        <f>IF(K13="","",IF(K13&gt;=0.7,5,IF(K13&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="54">
       <c r="A14" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="17"/>
@@ -6895,20 +6896,20 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="9">
-        <f>IF(COUNTA(B14:J14)=0,"",MIN(1,(IF(ISNUMBER(B14),MIN(B14/500000,1),0)+IF(ISNUMBER(C14),MIN(C14/60,1),0)+IF(ISNUMBER(D14),D14/5,0)+IF(ISNUMBER(E14),E14/5,0)+IF(F14="да",1,0)+IF(G14="да",1,0)+IF(ISNUMBER(H14),MIN(H14/50,1),0)+IF(ISNUMBER(I14),MIN(I14/6,1),0)+IF(ISNUMBER(J14),IF(J14&gt;0,1,0),0))/MAX(1,ISNUMBER(B14)+ISNUMBER(C14)+ISNUMBER(D14)+ISNUMBER(E14)+(F14&lt;&gt;"")+(G14&lt;&gt;"")+ISNUMBER(H14)+ISNUMBER(I14)+ISNUMBER(J14))))</f>
+        <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="L14" s="18">
-        <f>IF(K14="","",IF(K14&gt;=0.7,5,IF(K14&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54">
       <c r="A15" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="17"/>
@@ -6924,15 +6925,15 @@
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="9">
-        <f>IF(COUNTA(B15:J15)=0,"",MIN(1,(IF(ISNUMBER(B15),MIN(B15/500000,1),0)+IF(ISNUMBER(C15),MIN(C15/60,1),0)+IF(ISNUMBER(D15),D15/5,0)+IF(ISNUMBER(E15),E15/5,0)+IF(F15="да",1,0)+IF(G15="да",1,0)+IF(ISNUMBER(H15),MIN(H15/50,1),0)+IF(ISNUMBER(I15),MIN(I15/6,1),0)+IF(ISNUMBER(J15),IF(J15&gt;0,1,0),0))/MAX(1,ISNUMBER(B15)+ISNUMBER(C15)+ISNUMBER(D15)+ISNUMBER(E15)+(F15&lt;&gt;"")+(G15&lt;&gt;"")+ISNUMBER(H15)+ISNUMBER(I15)+ISNUMBER(J15))))</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="L15" s="18">
-        <f>IF(K15="","",IF(K15&gt;=0.7,5,IF(K15&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -6947,11 +6948,11 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="9" t="str">
-        <f>IF(COUNTA(B16:J16)=0,"",MIN(1,(IF(ISNUMBER(B16),MIN(B16/500000,1),0)+IF(ISNUMBER(C16),MIN(C16/60,1),0)+IF(ISNUMBER(D16),D16/5,0)+IF(ISNUMBER(E16),E16/5,0)+IF(F16="да",1,0)+IF(G16="да",1,0)+IF(ISNUMBER(H16),MIN(H16/50,1),0)+IF(ISNUMBER(I16),MIN(I16/6,1),0)+IF(ISNUMBER(J16),IF(J16&gt;0,1,0),0))/MAX(1,ISNUMBER(B16)+ISNUMBER(C16)+ISNUMBER(D16)+ISNUMBER(E16)+(F16&lt;&gt;"")+(G16&lt;&gt;"")+ISNUMBER(H16)+ISNUMBER(I16)+ISNUMBER(J16))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L16" s="18" t="str">
-        <f>IF(K16="","",IF(K16&gt;=0.7,5,IF(K16&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M16" s="2"/>
@@ -6968,11 +6969,11 @@
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="9" t="str">
-        <f>IF(COUNTA(B17:J17)=0,"",MIN(1,(IF(ISNUMBER(B17),MIN(B17/500000,1),0)+IF(ISNUMBER(C17),MIN(C17/60,1),0)+IF(ISNUMBER(D17),D17/5,0)+IF(ISNUMBER(E17),E17/5,0)+IF(F17="да",1,0)+IF(G17="да",1,0)+IF(ISNUMBER(H17),MIN(H17/50,1),0)+IF(ISNUMBER(I17),MIN(I17/6,1),0)+IF(ISNUMBER(J17),IF(J17&gt;0,1,0),0))/MAX(1,ISNUMBER(B17)+ISNUMBER(C17)+ISNUMBER(D17)+ISNUMBER(E17)+(F17&lt;&gt;"")+(G17&lt;&gt;"")+ISNUMBER(H17)+ISNUMBER(I17)+ISNUMBER(J17))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L17" s="18" t="str">
-        <f>IF(K17="","",IF(K17&gt;=0.7,5,IF(K17&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M17" s="2"/>
@@ -6989,11 +6990,11 @@
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="9" t="str">
-        <f>IF(COUNTA(B18:J18)=0,"",MIN(1,(IF(ISNUMBER(B18),MIN(B18/500000,1),0)+IF(ISNUMBER(C18),MIN(C18/60,1),0)+IF(ISNUMBER(D18),D18/5,0)+IF(ISNUMBER(E18),E18/5,0)+IF(F18="да",1,0)+IF(G18="да",1,0)+IF(ISNUMBER(H18),MIN(H18/50,1),0)+IF(ISNUMBER(I18),MIN(I18/6,1),0)+IF(ISNUMBER(J18),IF(J18&gt;0,1,0),0))/MAX(1,ISNUMBER(B18)+ISNUMBER(C18)+ISNUMBER(D18)+ISNUMBER(E18)+(F18&lt;&gt;"")+(G18&lt;&gt;"")+ISNUMBER(H18)+ISNUMBER(I18)+ISNUMBER(J18))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L18" s="18" t="str">
-        <f>IF(K18="","",IF(K18&gt;=0.7,5,IF(K18&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M18" s="2"/>
@@ -7010,11 +7011,11 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="9" t="str">
-        <f>IF(COUNTA(B19:J19)=0,"",MIN(1,(IF(ISNUMBER(B19),MIN(B19/500000,1),0)+IF(ISNUMBER(C19),MIN(C19/60,1),0)+IF(ISNUMBER(D19),D19/5,0)+IF(ISNUMBER(E19),E19/5,0)+IF(F19="да",1,0)+IF(G19="да",1,0)+IF(ISNUMBER(H19),MIN(H19/50,1),0)+IF(ISNUMBER(I19),MIN(I19/6,1),0)+IF(ISNUMBER(J19),IF(J19&gt;0,1,0),0))/MAX(1,ISNUMBER(B19)+ISNUMBER(C19)+ISNUMBER(D19)+ISNUMBER(E19)+(F19&lt;&gt;"")+(G19&lt;&gt;"")+ISNUMBER(H19)+ISNUMBER(I19)+ISNUMBER(J19))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L19" s="18" t="str">
-        <f>IF(K19="","",IF(K19&gt;=0.7,5,IF(K19&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M19" s="2"/>
@@ -7031,11 +7032,11 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="9" t="str">
-        <f>IF(COUNTA(B20:J20)=0,"",MIN(1,(IF(ISNUMBER(B20),MIN(B20/500000,1),0)+IF(ISNUMBER(C20),MIN(C20/60,1),0)+IF(ISNUMBER(D20),D20/5,0)+IF(ISNUMBER(E20),E20/5,0)+IF(F20="да",1,0)+IF(G20="да",1,0)+IF(ISNUMBER(H20),MIN(H20/50,1),0)+IF(ISNUMBER(I20),MIN(I20/6,1),0)+IF(ISNUMBER(J20),IF(J20&gt;0,1,0),0))/MAX(1,ISNUMBER(B20)+ISNUMBER(C20)+ISNUMBER(D20)+ISNUMBER(E20)+(F20&lt;&gt;"")+(G20&lt;&gt;"")+ISNUMBER(H20)+ISNUMBER(I20)+ISNUMBER(J20))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L20" s="18" t="str">
-        <f>IF(K20="","",IF(K20&gt;=0.7,5,IF(K20&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M20" s="2"/>
@@ -7052,11 +7053,11 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="9" t="str">
-        <f>IF(COUNTA(B21:J21)=0,"",MIN(1,(IF(ISNUMBER(B21),MIN(B21/500000,1),0)+IF(ISNUMBER(C21),MIN(C21/60,1),0)+IF(ISNUMBER(D21),D21/5,0)+IF(ISNUMBER(E21),E21/5,0)+IF(F21="да",1,0)+IF(G21="да",1,0)+IF(ISNUMBER(H21),MIN(H21/50,1),0)+IF(ISNUMBER(I21),MIN(I21/6,1),0)+IF(ISNUMBER(J21),IF(J21&gt;0,1,0),0))/MAX(1,ISNUMBER(B21)+ISNUMBER(C21)+ISNUMBER(D21)+ISNUMBER(E21)+(F21&lt;&gt;"")+(G21&lt;&gt;"")+ISNUMBER(H21)+ISNUMBER(I21)+ISNUMBER(J21))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L21" s="18" t="str">
-        <f>IF(K21="","",IF(K21&gt;=0.7,5,IF(K21&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M21" s="2"/>
@@ -7073,11 +7074,11 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="9" t="str">
-        <f>IF(COUNTA(B22:J22)=0,"",MIN(1,(IF(ISNUMBER(B22),MIN(B22/500000,1),0)+IF(ISNUMBER(C22),MIN(C22/60,1),0)+IF(ISNUMBER(D22),D22/5,0)+IF(ISNUMBER(E22),E22/5,0)+IF(F22="да",1,0)+IF(G22="да",1,0)+IF(ISNUMBER(H22),MIN(H22/50,1),0)+IF(ISNUMBER(I22),MIN(I22/6,1),0)+IF(ISNUMBER(J22),IF(J22&gt;0,1,0),0))/MAX(1,ISNUMBER(B22)+ISNUMBER(C22)+ISNUMBER(D22)+ISNUMBER(E22)+(F22&lt;&gt;"")+(G22&lt;&gt;"")+ISNUMBER(H22)+ISNUMBER(I22)+ISNUMBER(J22))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L22" s="18" t="str">
-        <f>IF(K22="","",IF(K22&gt;=0.7,5,IF(K22&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M22" s="2"/>
@@ -7094,11 +7095,11 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="9" t="str">
-        <f>IF(COUNTA(B23:J23)=0,"",MIN(1,(IF(ISNUMBER(B23),MIN(B23/500000,1),0)+IF(ISNUMBER(C23),MIN(C23/60,1),0)+IF(ISNUMBER(D23),D23/5,0)+IF(ISNUMBER(E23),E23/5,0)+IF(F23="да",1,0)+IF(G23="да",1,0)+IF(ISNUMBER(H23),MIN(H23/50,1),0)+IF(ISNUMBER(I23),MIN(I23/6,1),0)+IF(ISNUMBER(J23),IF(J23&gt;0,1,0),0))/MAX(1,ISNUMBER(B23)+ISNUMBER(C23)+ISNUMBER(D23)+ISNUMBER(E23)+(F23&lt;&gt;"")+(G23&lt;&gt;"")+ISNUMBER(H23)+ISNUMBER(I23)+ISNUMBER(J23))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L23" s="18" t="str">
-        <f>IF(K23="","",IF(K23&gt;=0.7,5,IF(K23&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M23" s="2"/>
@@ -7115,11 +7116,11 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="9" t="str">
-        <f>IF(COUNTA(B24:J24)=0,"",MIN(1,(IF(ISNUMBER(B24),MIN(B24/500000,1),0)+IF(ISNUMBER(C24),MIN(C24/60,1),0)+IF(ISNUMBER(D24),D24/5,0)+IF(ISNUMBER(E24),E24/5,0)+IF(F24="да",1,0)+IF(G24="да",1,0)+IF(ISNUMBER(H24),MIN(H24/50,1),0)+IF(ISNUMBER(I24),MIN(I24/6,1),0)+IF(ISNUMBER(J24),IF(J24&gt;0,1,0),0))/MAX(1,ISNUMBER(B24)+ISNUMBER(C24)+ISNUMBER(D24)+ISNUMBER(E24)+(F24&lt;&gt;"")+(G24&lt;&gt;"")+ISNUMBER(H24)+ISNUMBER(I24)+ISNUMBER(J24))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L24" s="18" t="str">
-        <f>IF(K24="","",IF(K24&gt;=0.7,5,IF(K24&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M24" s="2"/>
@@ -7136,11 +7137,11 @@
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="9" t="str">
-        <f>IF(COUNTA(B25:J25)=0,"",MIN(1,(IF(ISNUMBER(B25),MIN(B25/500000,1),0)+IF(ISNUMBER(C25),MIN(C25/60,1),0)+IF(ISNUMBER(D25),D25/5,0)+IF(ISNUMBER(E25),E25/5,0)+IF(F25="да",1,0)+IF(G25="да",1,0)+IF(ISNUMBER(H25),MIN(H25/50,1),0)+IF(ISNUMBER(I25),MIN(I25/6,1),0)+IF(ISNUMBER(J25),IF(J25&gt;0,1,0),0))/MAX(1,ISNUMBER(B25)+ISNUMBER(C25)+ISNUMBER(D25)+ISNUMBER(E25)+(F25&lt;&gt;"")+(G25&lt;&gt;"")+ISNUMBER(H25)+ISNUMBER(I25)+ISNUMBER(J25))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L25" s="18" t="str">
-        <f>IF(K25="","",IF(K25&gt;=0.7,5,IF(K25&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M25" s="2"/>
@@ -7157,11 +7158,11 @@
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="K26" s="9" t="str">
-        <f>IF(COUNTA(B26:J26)=0,"",MIN(1,(IF(ISNUMBER(B26),MIN(B26/500000,1),0)+IF(ISNUMBER(C26),MIN(C26/60,1),0)+IF(ISNUMBER(D26),D26/5,0)+IF(ISNUMBER(E26),E26/5,0)+IF(F26="да",1,0)+IF(G26="да",1,0)+IF(ISNUMBER(H26),MIN(H26/50,1),0)+IF(ISNUMBER(I26),MIN(I26/6,1),0)+IF(ISNUMBER(J26),IF(J26&gt;0,1,0),0))/MAX(1,ISNUMBER(B26)+ISNUMBER(C26)+ISNUMBER(D26)+ISNUMBER(E26)+(F26&lt;&gt;"")+(G26&lt;&gt;"")+ISNUMBER(H26)+ISNUMBER(I26)+ISNUMBER(J26))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L26" s="18" t="str">
-        <f>IF(K26="","",IF(K26&gt;=0.7,5,IF(K26&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M26" s="2"/>
@@ -7178,11 +7179,11 @@
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="9" t="str">
-        <f>IF(COUNTA(B27:J27)=0,"",MIN(1,(IF(ISNUMBER(B27),MIN(B27/500000,1),0)+IF(ISNUMBER(C27),MIN(C27/60,1),0)+IF(ISNUMBER(D27),D27/5,0)+IF(ISNUMBER(E27),E27/5,0)+IF(F27="да",1,0)+IF(G27="да",1,0)+IF(ISNUMBER(H27),MIN(H27/50,1),0)+IF(ISNUMBER(I27),MIN(I27/6,1),0)+IF(ISNUMBER(J27),IF(J27&gt;0,1,0),0))/MAX(1,ISNUMBER(B27)+ISNUMBER(C27)+ISNUMBER(D27)+ISNUMBER(E27)+(F27&lt;&gt;"")+(G27&lt;&gt;"")+ISNUMBER(H27)+ISNUMBER(I27)+ISNUMBER(J27))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L27" s="18" t="str">
-        <f>IF(K27="","",IF(K27&gt;=0.7,5,IF(K27&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M27" s="2"/>
@@ -7199,11 +7200,11 @@
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="9" t="str">
-        <f>IF(COUNTA(B28:J28)=0,"",MIN(1,(IF(ISNUMBER(B28),MIN(B28/500000,1),0)+IF(ISNUMBER(C28),MIN(C28/60,1),0)+IF(ISNUMBER(D28),D28/5,0)+IF(ISNUMBER(E28),E28/5,0)+IF(F28="да",1,0)+IF(G28="да",1,0)+IF(ISNUMBER(H28),MIN(H28/50,1),0)+IF(ISNUMBER(I28),MIN(I28/6,1),0)+IF(ISNUMBER(J28),IF(J28&gt;0,1,0),0))/MAX(1,ISNUMBER(B28)+ISNUMBER(C28)+ISNUMBER(D28)+ISNUMBER(E28)+(F28&lt;&gt;"")+(G28&lt;&gt;"")+ISNUMBER(H28)+ISNUMBER(I28)+ISNUMBER(J28))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L28" s="18" t="str">
-        <f>IF(K28="","",IF(K28&gt;=0.7,5,IF(K28&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M28" s="2"/>
@@ -7220,11 +7221,11 @@
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="K29" s="9" t="str">
-        <f>IF(COUNTA(B29:J29)=0,"",MIN(1,(IF(ISNUMBER(B29),MIN(B29/500000,1),0)+IF(ISNUMBER(C29),MIN(C29/60,1),0)+IF(ISNUMBER(D29),D29/5,0)+IF(ISNUMBER(E29),E29/5,0)+IF(F29="да",1,0)+IF(G29="да",1,0)+IF(ISNUMBER(H29),MIN(H29/50,1),0)+IF(ISNUMBER(I29),MIN(I29/6,1),0)+IF(ISNUMBER(J29),IF(J29&gt;0,1,0),0))/MAX(1,ISNUMBER(B29)+ISNUMBER(C29)+ISNUMBER(D29)+ISNUMBER(E29)+(F29&lt;&gt;"")+(G29&lt;&gt;"")+ISNUMBER(H29)+ISNUMBER(I29)+ISNUMBER(J29))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L29" s="18" t="str">
-        <f>IF(K29="","",IF(K29&gt;=0.7,5,IF(K29&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M29" s="2"/>
@@ -7241,11 +7242,11 @@
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="9" t="str">
-        <f>IF(COUNTA(B30:J30)=0,"",MIN(1,(IF(ISNUMBER(B30),MIN(B30/500000,1),0)+IF(ISNUMBER(C30),MIN(C30/60,1),0)+IF(ISNUMBER(D30),D30/5,0)+IF(ISNUMBER(E30),E30/5,0)+IF(F30="да",1,0)+IF(G30="да",1,0)+IF(ISNUMBER(H30),MIN(H30/50,1),0)+IF(ISNUMBER(I30),MIN(I30/6,1),0)+IF(ISNUMBER(J30),IF(J30&gt;0,1,0),0))/MAX(1,ISNUMBER(B30)+ISNUMBER(C30)+ISNUMBER(D30)+ISNUMBER(E30)+(F30&lt;&gt;"")+(G30&lt;&gt;"")+ISNUMBER(H30)+ISNUMBER(I30)+ISNUMBER(J30))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L30" s="18" t="str">
-        <f>IF(K30="","",IF(K30&gt;=0.7,5,IF(K30&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M30" s="2"/>
@@ -7262,11 +7263,11 @@
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="9" t="str">
-        <f>IF(COUNTA(B31:J31)=0,"",MIN(1,(IF(ISNUMBER(B31),MIN(B31/500000,1),0)+IF(ISNUMBER(C31),MIN(C31/60,1),0)+IF(ISNUMBER(D31),D31/5,0)+IF(ISNUMBER(E31),E31/5,0)+IF(F31="да",1,0)+IF(G31="да",1,0)+IF(ISNUMBER(H31),MIN(H31/50,1),0)+IF(ISNUMBER(I31),MIN(I31/6,1),0)+IF(ISNUMBER(J31),IF(J31&gt;0,1,0),0))/MAX(1,ISNUMBER(B31)+ISNUMBER(C31)+ISNUMBER(D31)+ISNUMBER(E31)+(F31&lt;&gt;"")+(G31&lt;&gt;"")+ISNUMBER(H31)+ISNUMBER(I31)+ISNUMBER(J31))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L31" s="18" t="str">
-        <f>IF(K31="","",IF(K31&gt;=0.7,5,IF(K31&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M31" s="2"/>
@@ -7283,11 +7284,11 @@
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="9" t="str">
-        <f>IF(COUNTA(B32:J32)=0,"",MIN(1,(IF(ISNUMBER(B32),MIN(B32/500000,1),0)+IF(ISNUMBER(C32),MIN(C32/60,1),0)+IF(ISNUMBER(D32),D32/5,0)+IF(ISNUMBER(E32),E32/5,0)+IF(F32="да",1,0)+IF(G32="да",1,0)+IF(ISNUMBER(H32),MIN(H32/50,1),0)+IF(ISNUMBER(I32),MIN(I32/6,1),0)+IF(ISNUMBER(J32),IF(J32&gt;0,1,0),0))/MAX(1,ISNUMBER(B32)+ISNUMBER(C32)+ISNUMBER(D32)+ISNUMBER(E32)+(F32&lt;&gt;"")+(G32&lt;&gt;"")+ISNUMBER(H32)+ISNUMBER(I32)+ISNUMBER(J32))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L32" s="18" t="str">
-        <f>IF(K32="","",IF(K32&gt;=0.7,5,IF(K32&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M32" s="2"/>
@@ -7304,11 +7305,11 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="9" t="str">
-        <f>IF(COUNTA(B33:J33)=0,"",MIN(1,(IF(ISNUMBER(B33),MIN(B33/500000,1),0)+IF(ISNUMBER(C33),MIN(C33/60,1),0)+IF(ISNUMBER(D33),D33/5,0)+IF(ISNUMBER(E33),E33/5,0)+IF(F33="да",1,0)+IF(G33="да",1,0)+IF(ISNUMBER(H33),MIN(H33/50,1),0)+IF(ISNUMBER(I33),MIN(I33/6,1),0)+IF(ISNUMBER(J33),IF(J33&gt;0,1,0),0))/MAX(1,ISNUMBER(B33)+ISNUMBER(C33)+ISNUMBER(D33)+ISNUMBER(E33)+(F33&lt;&gt;"")+(G33&lt;&gt;"")+ISNUMBER(H33)+ISNUMBER(I33)+ISNUMBER(J33))))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L33" s="18" t="str">
-        <f>IF(K33="","",IF(K33&gt;=0.7,5,IF(K33&gt;=0.4,3,1)))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M33" s="2"/>
@@ -7403,30 +7404,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:9" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -7594,7 +7595,7 @@
         <v>251</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C8" s="9">
         <f>IF(ISNUMBER('04_Поиск_реклама'!B37),'04_Поиск_реклама'!B37,AVERAGE(MIN('03_Каналы_трафика'!C5/'01_Параметры'!B15,1),MIN('03_Каналы_трафика'!C6/'01_Параметры'!B14,1)))</f>
@@ -7693,7 +7694,7 @@
         <v>262</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C11" s="11">
         <v>0.6</v>
@@ -7725,7 +7726,7 @@
         <v>265</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C12" s="11">
         <f>IFERROR(1-SUMPRODUCT(('02_Конкуренты_SW'!B4:B33&lt;&gt;"")*(LEFT('02_Конкуренты_SW'!B4:B33,6)="прямой")*'02_Конкуренты_SW'!E4:E33)/SUM('02_Конкуренты_SW'!E4:E33),0)</f>
@@ -7778,7 +7779,7 @@
         <v>средние барьеры</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>269</v>
@@ -7834,36 +7835,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="16.05" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
     </row>
     <row r="4" spans="1:12" ht="17" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -8126,51 +8127,51 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="14" customHeight="1">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="27" t="s">
         <v>288</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="28" t="str">
+      <c r="A15" s="29" t="str">
         <f>"По результатам оценки цифровой конкуренции индекс барьеров входа составляет "&amp;ROUND(B5,2)&amp;" из 5, что соответствует уровню: "&amp;B6&amp;". "&amp;"Наиболее значимые факторы давления определены по листу 07_Барьеры_входа. "&amp;"Данные Similarweb и альтернативных источников являются оценочной базой и требуют проверки "&amp;"через фактические коммерческие данные, цены, конверсии и платежеспособность клиентов."</f>
         <v>По результатам оценки цифровой конкуренции индекс барьеров входа составляет 3,15 из 5, что соответствует уровню: средние барьеры. Наиболее значимые факторы давления определены по листу 07_Барьеры_входа. Данные Similarweb и альтернативных источников являются оценочной базой и требуют проверки через фактические коммерческие данные, цены, конверсии и платежеспособность клиентов.</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="28"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/ЛР4_Пять_сил_Портера/Excel/ЛР4_1_конкуренция_и_барьеры_входа_TableMind.xlsx
+++ b/ЛР4_Пять_сил_Портера/Excel/ЛР4_1_конкуренция_и_барьеры_входа_TableMind.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР4_Пять_сил_Портера\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-89518d\ЛР4_Пять_сил_Портера\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5C84AC7-77B7-485C-BE0E-026816F4A84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C86C34-53C1-4504-9CBA-F3D7913C539D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,6 @@
     <sheet name="09_Источники" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -967,9 +966,6 @@
     <t>таблица/скриншот/экспорт при доступе</t>
   </si>
   <si>
-    <t>часть данных платная, оценки модельные</t>
-  </si>
-  <si>
     <t>Ahrefs</t>
   </si>
   <si>
@@ -1375,13 +1371,16 @@
     <t>Similarweb Pro, 06-08.2026, 03.10.2026; брендовый поиск - доля прямых заходов как прокси</t>
   </si>
   <si>
-    <t>CPC, PPC, SEO difficulty, выдача и объявления: модельные показатели (отчет ЛР4, приложение Д, допущение Д-33)</t>
-  </si>
-  <si>
     <t>Среднее число отзывов на конкурента (G2, Capterra, Trustpilot); отзывы Google, кейсы и возраст бренда - по сайтам конкурентов</t>
   </si>
   <si>
     <t>D и E - экспертные баллы (Д-17); финансирование и штат - по открытым источникам (ЛР5, приложение Д)</t>
+  </si>
+  <si>
+    <t>CPC, PPC, SEO difficulty, выдача и объявления: расчетные показатели (отчет ЛР4, приложение Д, допущение Д-33)</t>
+  </si>
+  <si>
+    <t>часть данных платная, оценки расчетные</t>
   </si>
 </sst>
 </file>
@@ -2476,329 +2475,329 @@
         <v>46298</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>307</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="27">
       <c r="A6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="F6" s="24">
         <v>46298</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="27">
       <c r="A7" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="F7" s="24">
         <v>46298</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="F8" s="24">
         <v>46298</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="F9" s="24">
         <v>46298</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="F10" s="24">
         <v>46298</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="F11" s="24">
         <v>46298</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="D12" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="F12" s="24">
         <v>46298</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="F13" s="24">
         <v>46298</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="27">
       <c r="A14" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="F14" s="24">
         <v>46298</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>362</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F15" s="24">
         <v>46298</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>367</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F16" s="24">
         <v>46298</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="F17" s="24">
         <v>46298</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="27">
       <c r="A18" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="F18" s="24">
         <v>46298</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="27">
       <c r="A19" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="F19" s="24">
         <v>46298</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -2870,7 +2869,7 @@
         <v>62</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
@@ -2886,7 +2885,7 @@
         <v>65</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
@@ -2902,7 +2901,7 @@
         <v>67</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -2921,13 +2920,13 @@
         <v>46298</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -2946,7 +2945,7 @@
         <v>72</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>12</v>
@@ -2967,7 +2966,7 @@
         <v>72</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>12</v>
@@ -3198,7 +3197,7 @@
         <v>99</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>100</v>
@@ -3242,10 +3241,10 @@
     </row>
     <row r="4" spans="1:17" ht="54">
       <c r="A4" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>396</v>
       </c>
       <c r="C4" s="10">
         <v>154111</v>
@@ -3288,15 +3287,15 @@
       </c>
       <c r="P4" s="11"/>
       <c r="Q4" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="54">
       <c r="A5" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>398</v>
       </c>
       <c r="C5" s="10">
         <v>35325</v>
@@ -3341,15 +3340,15 @@
       </c>
       <c r="P5" s="11"/>
       <c r="Q5" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="54">
       <c r="A6" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>400</v>
       </c>
       <c r="C6" s="10">
         <v>241737</v>
@@ -3394,15 +3393,15 @@
       </c>
       <c r="P6" s="11"/>
       <c r="Q6" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="54">
       <c r="A7" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>402</v>
       </c>
       <c r="C7" s="10">
         <v>202178</v>
@@ -3447,15 +3446,15 @@
       </c>
       <c r="P7" s="11"/>
       <c r="Q7" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="54">
       <c r="A8" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="C8" s="10">
         <v>14688</v>
@@ -3500,15 +3499,15 @@
       </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="54">
       <c r="A9" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C9" s="10">
         <v>17824</v>
@@ -3553,15 +3552,15 @@
       </c>
       <c r="P9" s="11"/>
       <c r="Q9" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="54">
       <c r="A10" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C10" s="10">
         <v>292214</v>
@@ -3606,15 +3605,15 @@
       </c>
       <c r="P10" s="11"/>
       <c r="Q10" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="54">
       <c r="A11" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C11" s="10">
         <v>116617</v>
@@ -3659,15 +3658,15 @@
       </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="54">
       <c r="A12" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>409</v>
       </c>
       <c r="C12" s="10">
         <v>222359</v>
@@ -3712,15 +3711,15 @@
       </c>
       <c r="P12" s="11"/>
       <c r="Q12" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="54">
       <c r="A13" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>411</v>
       </c>
       <c r="C13" s="10">
         <v>701540</v>
@@ -3765,15 +3764,15 @@
       </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="54">
       <c r="A14" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C14" s="10">
         <v>1935</v>
@@ -3818,15 +3817,15 @@
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="54">
       <c r="A15" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>414</v>
       </c>
       <c r="C15" s="10">
         <v>5522</v>
@@ -3871,7 +3870,7 @@
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -4787,7 +4786,7 @@
         <v>133</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>177</v>
@@ -4819,13 +4818,13 @@
     </row>
     <row r="4" spans="1:13" ht="67.5">
       <c r="A4" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>184</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D4" s="10">
         <v>47.6</v>
@@ -4845,18 +4844,18 @@
         <v/>
       </c>
       <c r="M4" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="67.5">
       <c r="A5" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>184</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D5" s="10">
         <v>32</v>
@@ -4876,18 +4875,18 @@
         <v/>
       </c>
       <c r="M5" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="67.5">
       <c r="A6" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>185</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D6" s="10">
         <v>13.2</v>
@@ -4907,18 +4906,18 @@
         <v/>
       </c>
       <c r="M6" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="67.5">
       <c r="A7" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>184</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D7" s="10">
         <v>29</v>
@@ -4938,18 +4937,18 @@
         <v/>
       </c>
       <c r="M7" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="67.5">
       <c r="A8" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>421</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D8" s="10">
         <v>60.9</v>
@@ -4969,18 +4968,18 @@
         <v/>
       </c>
       <c r="M8" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="67.5">
       <c r="A9" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>423</v>
-      </c>
       <c r="C9" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D9" s="10">
         <v>0.6</v>
@@ -5000,7 +4999,7 @@
         <v/>
       </c>
       <c r="M9" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5558,7 +5557,7 @@
         <v>192</v>
       </c>
       <c r="D39" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -5686,7 +5685,7 @@
     </row>
     <row r="4" spans="1:14" ht="40.5">
       <c r="A4" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="10"/>
@@ -5707,12 +5706,12 @@
         <v/>
       </c>
       <c r="N4" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27">
       <c r="A5" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="10">
@@ -5737,12 +5736,12 @@
         <v>1</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B6" s="19">
         <v>4.9000000000000004</v>
@@ -5767,12 +5766,12 @@
         <v>3</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="27">
       <c r="A7" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="10"/>
@@ -5793,12 +5792,12 @@
         <v/>
       </c>
       <c r="N7" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="54">
       <c r="A8" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="10"/>
@@ -5819,12 +5818,12 @@
         <v/>
       </c>
       <c r="N8" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B9" s="19">
         <v>4</v>
@@ -5849,12 +5848,12 @@
         <v>3</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B10" s="19">
         <v>4.5</v>
@@ -5879,12 +5878,12 @@
         <v>3</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B11" s="19">
         <v>4.5</v>
@@ -5909,12 +5908,12 @@
         <v>3</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B12" s="19">
         <v>4.5999999999999996</v>
@@ -5939,12 +5938,12 @@
         <v>5</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B13" s="19">
         <v>4.5</v>
@@ -5969,12 +5968,12 @@
         <v>3</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="10">
@@ -5997,12 +5996,12 @@
         <v>1</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="27">
       <c r="A15" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B15" s="19">
         <v>4.7</v>
@@ -6027,7 +6026,7 @@
         <v>3</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -6469,7 +6468,7 @@
         <v>низкий барьер</v>
       </c>
       <c r="D38" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -6590,7 +6589,7 @@
     </row>
     <row r="4" spans="1:13" ht="54">
       <c r="A4" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="17"/>
@@ -6614,12 +6613,12 @@
         <v>5</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54">
       <c r="A5" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="17"/>
@@ -6643,12 +6642,12 @@
         <v>3</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="54">
       <c r="A6" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="17"/>
@@ -6672,12 +6671,12 @@
         <v>5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54">
       <c r="A7" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="17"/>
@@ -6701,12 +6700,12 @@
         <v>5</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54">
       <c r="A8" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="17"/>
@@ -6730,12 +6729,12 @@
         <v>3</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="54">
       <c r="A9" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="17"/>
@@ -6759,12 +6758,12 @@
         <v>3</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="54">
       <c r="A10" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="17"/>
@@ -6788,12 +6787,12 @@
         <v>3</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="54">
       <c r="A11" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="17"/>
@@ -6817,12 +6816,12 @@
         <v>3</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54">
       <c r="A12" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="17"/>
@@ -6846,12 +6845,12 @@
         <v>5</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="54">
       <c r="A13" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="17"/>
@@ -6875,12 +6874,12 @@
         <v>5</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="54">
       <c r="A14" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="17"/>
@@ -6904,12 +6903,12 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54">
       <c r="A15" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="17"/>
@@ -6933,7 +6932,7 @@
         <v>5</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -7595,7 +7594,7 @@
         <v>251</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C8" s="9">
         <f>IF(ISNUMBER('04_Поиск_реклама'!B37),'04_Поиск_реклама'!B37,AVERAGE(MIN('03_Каналы_трафика'!C5/'01_Параметры'!B15,1),MIN('03_Каналы_трафика'!C6/'01_Параметры'!B14,1)))</f>
@@ -7694,7 +7693,7 @@
         <v>262</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C11" s="11">
         <v>0.6</v>
@@ -7726,7 +7725,7 @@
         <v>265</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C12" s="11">
         <f>IFERROR(1-SUMPRODUCT(('02_Конкуренты_SW'!B4:B33&lt;&gt;"")*(LEFT('02_Конкуренты_SW'!B4:B33,6)="прямой")*'02_Конкуренты_SW'!E4:E33)/SUM('02_Конкуренты_SW'!E4:E33),0)</f>
@@ -7779,7 +7778,7 @@
         <v>средние барьеры</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>269</v>

--- a/ЛР4_Пять_сил_Портера/Excel/ЛР4_1_конкуренция_и_барьеры_входа_TableMind.xlsx
+++ b/ЛР4_Пять_сил_Портера/Excel/ЛР4_1_конкуренция_и_барьеры_входа_TableMind.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР4_Пять_сил_Портера\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР4_Пять_сил_Портера\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5C84AC7-77B7-485C-BE0E-026816F4A84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B157B6F4-2600-4FA7-AACF-6FB7D87A73CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,6 @@
     <sheet name="09_Источники" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1237,6 +1236,9 @@
     <t>частичный конкурент: AI-агент для Excel</t>
   </si>
   <si>
+    <t>Similarweb Pro, 06-08.2026, 03.10.2026; брендовый поиск не снимался</t>
+  </si>
+  <si>
     <t>perfectxl.com</t>
   </si>
   <si>
@@ -1297,6 +1299,9 @@
     <t>Google Trends (индекс 0-100, ЛР1)</t>
   </si>
   <si>
+    <t>CPC, PPC и SEO difficulty: данные Similarweb Keyword research для 5 массовых запросов (приложение Д), остальное - модельные показатели</t>
+  </si>
+  <si>
     <t>spreadsheet audit</t>
   </si>
   <si>
@@ -1360,6 +1365,12 @@
     <t>G2: CIMCON Software (EUC-риск)</t>
   </si>
   <si>
+    <t>Среднее число отзывов на конкурента (G2, Capterra, Trustpilot); отзывы Google, кейсы и возраст бренда - ДОСНЯТЬ</t>
+  </si>
+  <si>
+    <t>D и E - экспертные баллы (Д-17); финансирование и штат - деловая пресса (приложение Д ЛР5), вакансии и объявления не собирались</t>
+  </si>
+  <si>
     <t>CPC, PPC, SEO difficulty (при отсутствии - прокси: органика и платный поиск Similarweb к порогам)</t>
   </si>
   <si>
@@ -1370,18 +1381,6 @@
   </si>
   <si>
     <t>Интегральная оценка давления (сумма весов в шаблоне 1,04, поэтому делится на сумму весов).</t>
-  </si>
-  <si>
-    <t>Similarweb Pro, 06-08.2026, 03.10.2026; брендовый поиск - доля прямых заходов как прокси</t>
-  </si>
-  <si>
-    <t>CPC, PPC, SEO difficulty, выдача и объявления: модельные показатели (отчет ЛР4, приложение Д, допущение Д-33)</t>
-  </si>
-  <si>
-    <t>Среднее число отзывов на конкурента (G2, Capterra, Trustpilot); отзывы Google, кейсы и возраст бренда - по сайтам конкурентов</t>
-  </si>
-  <si>
-    <t>D и E - экспертные баллы (Д-17); финансирование и штат - по открытым источникам (ЛР5, приложение Д)</t>
   </si>
 </sst>
 </file>
@@ -1538,9 +1537,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1555,6 +1551,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1682,7 +1681,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5A3D-49C7-B849-BF42B6EE74CB}"/>
+              <c16:uniqueId val="{00000000-82D8-40F4-AACF-D8E1310D3C3B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2109,30 +2108,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="4" spans="1:9" ht="17" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -2305,63 +2304,63 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14" customHeight="1">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2389,26 +2388,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>289</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>290</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" spans="1:7" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -2449,7 +2448,7 @@
       <c r="E4" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="29">
         <v>46298</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -2472,7 +2471,7 @@
       <c r="E5" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="29">
         <v>46298</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -2495,7 +2494,7 @@
       <c r="E6" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="29">
         <v>46298</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -2518,7 +2517,7 @@
       <c r="E7" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="29">
         <v>46298</v>
       </c>
       <c r="G7" s="2" t="s">
@@ -2541,7 +2540,7 @@
       <c r="E8" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="29">
         <v>46298</v>
       </c>
       <c r="G8" s="2" t="s">
@@ -2564,7 +2563,7 @@
       <c r="E9" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="29">
         <v>46298</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -2587,7 +2586,7 @@
       <c r="E10" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="29">
         <v>46298</v>
       </c>
       <c r="G10" s="2" t="s">
@@ -2610,7 +2609,7 @@
       <c r="E11" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="29">
         <v>46298</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -2633,7 +2632,7 @@
       <c r="E12" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="29">
         <v>46298</v>
       </c>
       <c r="G12" s="2" t="s">
@@ -2656,7 +2655,7 @@
       <c r="E13" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="29">
         <v>46298</v>
       </c>
       <c r="G13" s="2" t="s">
@@ -2679,7 +2678,7 @@
       <c r="E14" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="29">
         <v>46298</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -2702,7 +2701,7 @@
       <c r="E15" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="29">
         <v>46298</v>
       </c>
       <c r="G15" s="2" t="s">
@@ -2725,7 +2724,7 @@
       <c r="E16" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="29">
         <v>46298</v>
       </c>
       <c r="G16" s="2" t="s">
@@ -2748,7 +2747,7 @@
       <c r="E17" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="29">
         <v>46298</v>
       </c>
       <c r="G17" s="2" t="s">
@@ -2771,7 +2770,7 @@
       <c r="E18" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="29">
         <v>46298</v>
       </c>
       <c r="G18" s="2" t="s">
@@ -2794,7 +2793,7 @@
       <c r="E19" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="29">
         <v>46298</v>
       </c>
       <c r="G19" s="2" t="s">
@@ -2826,24 +2825,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" ht="16.05" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
     </row>
     <row r="4" spans="1:6" ht="17" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -3146,46 +3145,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
     </row>
     <row r="2" spans="1:17" ht="16.05" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
     </row>
     <row r="3" spans="1:17" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -3240,7 +3239,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="54">
+    <row r="4" spans="1:17" ht="40.5">
       <c r="A4" s="4" t="s">
         <v>395</v>
       </c>
@@ -3288,15 +3287,15 @@
       </c>
       <c r="P4" s="11"/>
       <c r="Q4" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="54">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="40.5">
       <c r="A5" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C5" s="10">
         <v>35325</v>
@@ -3341,15 +3340,15 @@
       </c>
       <c r="P5" s="11"/>
       <c r="Q5" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="54">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="40.5">
       <c r="A6" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C6" s="10">
         <v>241737</v>
@@ -3394,15 +3393,15 @@
       </c>
       <c r="P6" s="11"/>
       <c r="Q6" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="54">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="40.5">
       <c r="A7" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C7" s="10">
         <v>202178</v>
@@ -3447,15 +3446,15 @@
       </c>
       <c r="P7" s="11"/>
       <c r="Q7" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="54">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="40.5">
       <c r="A8" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C8" s="10">
         <v>14688</v>
@@ -3500,15 +3499,15 @@
       </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="54">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="40.5">
       <c r="A9" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C9" s="10">
         <v>17824</v>
@@ -3553,15 +3552,15 @@
       </c>
       <c r="P9" s="11"/>
       <c r="Q9" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="54">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="40.5">
       <c r="A10" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C10" s="10">
         <v>292214</v>
@@ -3606,15 +3605,15 @@
       </c>
       <c r="P10" s="11"/>
       <c r="Q10" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="54">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="40.5">
       <c r="A11" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C11" s="10">
         <v>116617</v>
@@ -3659,15 +3658,15 @@
       </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="54">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="40.5">
       <c r="A12" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C12" s="10">
         <v>222359</v>
@@ -3712,15 +3711,15 @@
       </c>
       <c r="P12" s="11"/>
       <c r="Q12" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="54">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="40.5">
       <c r="A13" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C13" s="10">
         <v>701540</v>
@@ -3765,15 +3764,15 @@
       </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="54">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="40.5">
       <c r="A14" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C14" s="10">
         <v>1935</v>
@@ -3818,15 +3817,15 @@
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="54">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="40.5">
       <c r="A15" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C15" s="10">
         <v>5522</v>
@@ -3871,7 +3870,7 @@
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="4" t="s">
-        <v>442</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -4428,30 +4427,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -4743,38 +4742,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
     </row>
     <row r="2" spans="1:13" ht="16.05" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
     </row>
     <row r="3" spans="1:13" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -4787,7 +4786,7 @@
         <v>133</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>177</v>
@@ -4817,15 +4816,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="67.5">
+    <row r="4" spans="1:13" ht="81">
       <c r="A4" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>184</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D4" s="10">
         <v>47.6</v>
@@ -4837,26 +4836,26 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="9" t="str">
-        <f t="shared" ref="K4:K33" si="0">IF(COUNT(E4:J4)&lt;2,"",MIN(1,(IF(ISNUMBER(E4),MIN(E4/2,1),0)+IF(ISNUMBER(F4),F4,0)+IF(ISNUMBER(G4),G4/100,0)+IF(ISNUMBER(H4),MIN(H4/10,1),0)+IF(ISNUMBER(J4),MIN(J4/50,1),0))/MAX(1,COUNT(E4:H4,J4))))</f>
+        <f>IF(COUNT(E4:J4)&lt;2,"",MIN(1,(IF(ISNUMBER(E4),MIN(E4/2,1),0)+IF(ISNUMBER(F4),F4,0)+IF(ISNUMBER(G4),G4/100,0)+IF(ISNUMBER(H4),MIN(H4/10,1),0)+IF(ISNUMBER(J4),MIN(J4/50,1),0))/MAX(1,COUNT(E4:H4,J4))))</f>
         <v/>
       </c>
       <c r="L4" s="18" t="str">
-        <f t="shared" ref="L4:L33" si="1">IF(K4="","",IF(K4&gt;=0.7,5,IF(K4&gt;=0.4,3,1)))</f>
+        <f>IF(K4="","",IF(K4&gt;=0.7,5,IF(K4&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M4" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="67.5">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="81">
       <c r="A5" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>184</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D5" s="10">
         <v>32</v>
@@ -4868,26 +4867,26 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E5:J5)&lt;2,"",MIN(1,(IF(ISNUMBER(E5),MIN(E5/2,1),0)+IF(ISNUMBER(F5),F5,0)+IF(ISNUMBER(G5),G5/100,0)+IF(ISNUMBER(H5),MIN(H5/10,1),0)+IF(ISNUMBER(J5),MIN(J5/50,1),0))/MAX(1,COUNT(E5:H5,J5))))</f>
         <v/>
       </c>
       <c r="L5" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K5="","",IF(K5&gt;=0.7,5,IF(K5&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M5" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="67.5">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="81">
       <c r="A6" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>185</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D6" s="10">
         <v>13.2</v>
@@ -4899,26 +4898,26 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E6:J6)&lt;2,"",MIN(1,(IF(ISNUMBER(E6),MIN(E6/2,1),0)+IF(ISNUMBER(F6),F6,0)+IF(ISNUMBER(G6),G6/100,0)+IF(ISNUMBER(H6),MIN(H6/10,1),0)+IF(ISNUMBER(J6),MIN(J6/50,1),0))/MAX(1,COUNT(E6:H6,J6))))</f>
         <v/>
       </c>
       <c r="L6" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K6="","",IF(K6&gt;=0.7,5,IF(K6&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M6" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="67.5">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="81">
       <c r="A7" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>184</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D7" s="10">
         <v>29</v>
@@ -4930,26 +4929,26 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E7:J7)&lt;2,"",MIN(1,(IF(ISNUMBER(E7),MIN(E7/2,1),0)+IF(ISNUMBER(F7),F7,0)+IF(ISNUMBER(G7),G7/100,0)+IF(ISNUMBER(H7),MIN(H7/10,1),0)+IF(ISNUMBER(J7),MIN(J7/50,1),0))/MAX(1,COUNT(E7:H7,J7))))</f>
         <v/>
       </c>
       <c r="L7" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K7="","",IF(K7&gt;=0.7,5,IF(K7&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M7" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="67.5">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="81">
       <c r="A8" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D8" s="10">
         <v>60.9</v>
@@ -4961,26 +4960,26 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E8:J8)&lt;2,"",MIN(1,(IF(ISNUMBER(E8),MIN(E8/2,1),0)+IF(ISNUMBER(F8),F8,0)+IF(ISNUMBER(G8),G8/100,0)+IF(ISNUMBER(H8),MIN(H8/10,1),0)+IF(ISNUMBER(J8),MIN(J8/50,1),0))/MAX(1,COUNT(E8:H8,J8))))</f>
         <v/>
       </c>
       <c r="L8" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K8="","",IF(K8&gt;=0.7,5,IF(K8&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M8" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="67.5">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="81">
       <c r="A9" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D9" s="10">
         <v>0.6</v>
@@ -4992,15 +4991,15 @@
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E9:J9)&lt;2,"",MIN(1,(IF(ISNUMBER(E9),MIN(E9/2,1),0)+IF(ISNUMBER(F9),F9,0)+IF(ISNUMBER(G9),G9/100,0)+IF(ISNUMBER(H9),MIN(H9/10,1),0)+IF(ISNUMBER(J9),MIN(J9/50,1),0))/MAX(1,COUNT(E9:H9,J9))))</f>
         <v/>
       </c>
       <c r="L9" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K9="","",IF(K9&gt;=0.7,5,IF(K9&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M9" s="2" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5015,11 +5014,11 @@
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E10:J10)&lt;2,"",MIN(1,(IF(ISNUMBER(E10),MIN(E10/2,1),0)+IF(ISNUMBER(F10),F10,0)+IF(ISNUMBER(G10),G10/100,0)+IF(ISNUMBER(H10),MIN(H10/10,1),0)+IF(ISNUMBER(J10),MIN(J10/50,1),0))/MAX(1,COUNT(E10:H10,J10))))</f>
         <v/>
       </c>
       <c r="L10" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K10="","",IF(K10&gt;=0.7,5,IF(K10&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M10" s="2"/>
@@ -5036,11 +5035,11 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E11:J11)&lt;2,"",MIN(1,(IF(ISNUMBER(E11),MIN(E11/2,1),0)+IF(ISNUMBER(F11),F11,0)+IF(ISNUMBER(G11),G11/100,0)+IF(ISNUMBER(H11),MIN(H11/10,1),0)+IF(ISNUMBER(J11),MIN(J11/50,1),0))/MAX(1,COUNT(E11:H11,J11))))</f>
         <v/>
       </c>
       <c r="L11" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K11="","",IF(K11&gt;=0.7,5,IF(K11&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M11" s="2"/>
@@ -5057,11 +5056,11 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E12:J12)&lt;2,"",MIN(1,(IF(ISNUMBER(E12),MIN(E12/2,1),0)+IF(ISNUMBER(F12),F12,0)+IF(ISNUMBER(G12),G12/100,0)+IF(ISNUMBER(H12),MIN(H12/10,1),0)+IF(ISNUMBER(J12),MIN(J12/50,1),0))/MAX(1,COUNT(E12:H12,J12))))</f>
         <v/>
       </c>
       <c r="L12" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K12="","",IF(K12&gt;=0.7,5,IF(K12&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M12" s="2"/>
@@ -5078,11 +5077,11 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E13:J13)&lt;2,"",MIN(1,(IF(ISNUMBER(E13),MIN(E13/2,1),0)+IF(ISNUMBER(F13),F13,0)+IF(ISNUMBER(G13),G13/100,0)+IF(ISNUMBER(H13),MIN(H13/10,1),0)+IF(ISNUMBER(J13),MIN(J13/50,1),0))/MAX(1,COUNT(E13:H13,J13))))</f>
         <v/>
       </c>
       <c r="L13" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K13="","",IF(K13&gt;=0.7,5,IF(K13&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M13" s="2"/>
@@ -5099,11 +5098,11 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E14:J14)&lt;2,"",MIN(1,(IF(ISNUMBER(E14),MIN(E14/2,1),0)+IF(ISNUMBER(F14),F14,0)+IF(ISNUMBER(G14),G14/100,0)+IF(ISNUMBER(H14),MIN(H14/10,1),0)+IF(ISNUMBER(J14),MIN(J14/50,1),0))/MAX(1,COUNT(E14:H14,J14))))</f>
         <v/>
       </c>
       <c r="L14" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K14="","",IF(K14&gt;=0.7,5,IF(K14&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M14" s="2"/>
@@ -5120,11 +5119,11 @@
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E15:J15)&lt;2,"",MIN(1,(IF(ISNUMBER(E15),MIN(E15/2,1),0)+IF(ISNUMBER(F15),F15,0)+IF(ISNUMBER(G15),G15/100,0)+IF(ISNUMBER(H15),MIN(H15/10,1),0)+IF(ISNUMBER(J15),MIN(J15/50,1),0))/MAX(1,COUNT(E15:H15,J15))))</f>
         <v/>
       </c>
       <c r="L15" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K15="","",IF(K15&gt;=0.7,5,IF(K15&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M15" s="2"/>
@@ -5141,11 +5140,11 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E16:J16)&lt;2,"",MIN(1,(IF(ISNUMBER(E16),MIN(E16/2,1),0)+IF(ISNUMBER(F16),F16,0)+IF(ISNUMBER(G16),G16/100,0)+IF(ISNUMBER(H16),MIN(H16/10,1),0)+IF(ISNUMBER(J16),MIN(J16/50,1),0))/MAX(1,COUNT(E16:H16,J16))))</f>
         <v/>
       </c>
       <c r="L16" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K16="","",IF(K16&gt;=0.7,5,IF(K16&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M16" s="2"/>
@@ -5162,11 +5161,11 @@
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E17:J17)&lt;2,"",MIN(1,(IF(ISNUMBER(E17),MIN(E17/2,1),0)+IF(ISNUMBER(F17),F17,0)+IF(ISNUMBER(G17),G17/100,0)+IF(ISNUMBER(H17),MIN(H17/10,1),0)+IF(ISNUMBER(J17),MIN(J17/50,1),0))/MAX(1,COUNT(E17:H17,J17))))</f>
         <v/>
       </c>
       <c r="L17" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K17="","",IF(K17&gt;=0.7,5,IF(K17&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M17" s="2"/>
@@ -5183,11 +5182,11 @@
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E18:J18)&lt;2,"",MIN(1,(IF(ISNUMBER(E18),MIN(E18/2,1),0)+IF(ISNUMBER(F18),F18,0)+IF(ISNUMBER(G18),G18/100,0)+IF(ISNUMBER(H18),MIN(H18/10,1),0)+IF(ISNUMBER(J18),MIN(J18/50,1),0))/MAX(1,COUNT(E18:H18,J18))))</f>
         <v/>
       </c>
       <c r="L18" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K18="","",IF(K18&gt;=0.7,5,IF(K18&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M18" s="2"/>
@@ -5204,11 +5203,11 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E19:J19)&lt;2,"",MIN(1,(IF(ISNUMBER(E19),MIN(E19/2,1),0)+IF(ISNUMBER(F19),F19,0)+IF(ISNUMBER(G19),G19/100,0)+IF(ISNUMBER(H19),MIN(H19/10,1),0)+IF(ISNUMBER(J19),MIN(J19/50,1),0))/MAX(1,COUNT(E19:H19,J19))))</f>
         <v/>
       </c>
       <c r="L19" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K19="","",IF(K19&gt;=0.7,5,IF(K19&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M19" s="2"/>
@@ -5225,11 +5224,11 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E20:J20)&lt;2,"",MIN(1,(IF(ISNUMBER(E20),MIN(E20/2,1),0)+IF(ISNUMBER(F20),F20,0)+IF(ISNUMBER(G20),G20/100,0)+IF(ISNUMBER(H20),MIN(H20/10,1),0)+IF(ISNUMBER(J20),MIN(J20/50,1),0))/MAX(1,COUNT(E20:H20,J20))))</f>
         <v/>
       </c>
       <c r="L20" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K20="","",IF(K20&gt;=0.7,5,IF(K20&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M20" s="2"/>
@@ -5246,11 +5245,11 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E21:J21)&lt;2,"",MIN(1,(IF(ISNUMBER(E21),MIN(E21/2,1),0)+IF(ISNUMBER(F21),F21,0)+IF(ISNUMBER(G21),G21/100,0)+IF(ISNUMBER(H21),MIN(H21/10,1),0)+IF(ISNUMBER(J21),MIN(J21/50,1),0))/MAX(1,COUNT(E21:H21,J21))))</f>
         <v/>
       </c>
       <c r="L21" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K21="","",IF(K21&gt;=0.7,5,IF(K21&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M21" s="2"/>
@@ -5267,11 +5266,11 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E22:J22)&lt;2,"",MIN(1,(IF(ISNUMBER(E22),MIN(E22/2,1),0)+IF(ISNUMBER(F22),F22,0)+IF(ISNUMBER(G22),G22/100,0)+IF(ISNUMBER(H22),MIN(H22/10,1),0)+IF(ISNUMBER(J22),MIN(J22/50,1),0))/MAX(1,COUNT(E22:H22,J22))))</f>
         <v/>
       </c>
       <c r="L22" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K22="","",IF(K22&gt;=0.7,5,IF(K22&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M22" s="2"/>
@@ -5288,11 +5287,11 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E23:J23)&lt;2,"",MIN(1,(IF(ISNUMBER(E23),MIN(E23/2,1),0)+IF(ISNUMBER(F23),F23,0)+IF(ISNUMBER(G23),G23/100,0)+IF(ISNUMBER(H23),MIN(H23/10,1),0)+IF(ISNUMBER(J23),MIN(J23/50,1),0))/MAX(1,COUNT(E23:H23,J23))))</f>
         <v/>
       </c>
       <c r="L23" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K23="","",IF(K23&gt;=0.7,5,IF(K23&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M23" s="2"/>
@@ -5309,11 +5308,11 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E24:J24)&lt;2,"",MIN(1,(IF(ISNUMBER(E24),MIN(E24/2,1),0)+IF(ISNUMBER(F24),F24,0)+IF(ISNUMBER(G24),G24/100,0)+IF(ISNUMBER(H24),MIN(H24/10,1),0)+IF(ISNUMBER(J24),MIN(J24/50,1),0))/MAX(1,COUNT(E24:H24,J24))))</f>
         <v/>
       </c>
       <c r="L24" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K24="","",IF(K24&gt;=0.7,5,IF(K24&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M24" s="2"/>
@@ -5330,11 +5329,11 @@
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E25:J25)&lt;2,"",MIN(1,(IF(ISNUMBER(E25),MIN(E25/2,1),0)+IF(ISNUMBER(F25),F25,0)+IF(ISNUMBER(G25),G25/100,0)+IF(ISNUMBER(H25),MIN(H25/10,1),0)+IF(ISNUMBER(J25),MIN(J25/50,1),0))/MAX(1,COUNT(E25:H25,J25))))</f>
         <v/>
       </c>
       <c r="L25" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K25="","",IF(K25&gt;=0.7,5,IF(K25&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M25" s="2"/>
@@ -5351,11 +5350,11 @@
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="K26" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E26:J26)&lt;2,"",MIN(1,(IF(ISNUMBER(E26),MIN(E26/2,1),0)+IF(ISNUMBER(F26),F26,0)+IF(ISNUMBER(G26),G26/100,0)+IF(ISNUMBER(H26),MIN(H26/10,1),0)+IF(ISNUMBER(J26),MIN(J26/50,1),0))/MAX(1,COUNT(E26:H26,J26))))</f>
         <v/>
       </c>
       <c r="L26" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K26="","",IF(K26&gt;=0.7,5,IF(K26&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M26" s="2"/>
@@ -5372,11 +5371,11 @@
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E27:J27)&lt;2,"",MIN(1,(IF(ISNUMBER(E27),MIN(E27/2,1),0)+IF(ISNUMBER(F27),F27,0)+IF(ISNUMBER(G27),G27/100,0)+IF(ISNUMBER(H27),MIN(H27/10,1),0)+IF(ISNUMBER(J27),MIN(J27/50,1),0))/MAX(1,COUNT(E27:H27,J27))))</f>
         <v/>
       </c>
       <c r="L27" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K27="","",IF(K27&gt;=0.7,5,IF(K27&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M27" s="2"/>
@@ -5393,11 +5392,11 @@
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E28:J28)&lt;2,"",MIN(1,(IF(ISNUMBER(E28),MIN(E28/2,1),0)+IF(ISNUMBER(F28),F28,0)+IF(ISNUMBER(G28),G28/100,0)+IF(ISNUMBER(H28),MIN(H28/10,1),0)+IF(ISNUMBER(J28),MIN(J28/50,1),0))/MAX(1,COUNT(E28:H28,J28))))</f>
         <v/>
       </c>
       <c r="L28" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K28="","",IF(K28&gt;=0.7,5,IF(K28&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M28" s="2"/>
@@ -5414,11 +5413,11 @@
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="K29" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E29:J29)&lt;2,"",MIN(1,(IF(ISNUMBER(E29),MIN(E29/2,1),0)+IF(ISNUMBER(F29),F29,0)+IF(ISNUMBER(G29),G29/100,0)+IF(ISNUMBER(H29),MIN(H29/10,1),0)+IF(ISNUMBER(J29),MIN(J29/50,1),0))/MAX(1,COUNT(E29:H29,J29))))</f>
         <v/>
       </c>
       <c r="L29" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K29="","",IF(K29&gt;=0.7,5,IF(K29&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M29" s="2"/>
@@ -5435,11 +5434,11 @@
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E30:J30)&lt;2,"",MIN(1,(IF(ISNUMBER(E30),MIN(E30/2,1),0)+IF(ISNUMBER(F30),F30,0)+IF(ISNUMBER(G30),G30/100,0)+IF(ISNUMBER(H30),MIN(H30/10,1),0)+IF(ISNUMBER(J30),MIN(J30/50,1),0))/MAX(1,COUNT(E30:H30,J30))))</f>
         <v/>
       </c>
       <c r="L30" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K30="","",IF(K30&gt;=0.7,5,IF(K30&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M30" s="2"/>
@@ -5456,11 +5455,11 @@
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E31:J31)&lt;2,"",MIN(1,(IF(ISNUMBER(E31),MIN(E31/2,1),0)+IF(ISNUMBER(F31),F31,0)+IF(ISNUMBER(G31),G31/100,0)+IF(ISNUMBER(H31),MIN(H31/10,1),0)+IF(ISNUMBER(J31),MIN(J31/50,1),0))/MAX(1,COUNT(E31:H31,J31))))</f>
         <v/>
       </c>
       <c r="L31" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K31="","",IF(K31&gt;=0.7,5,IF(K31&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M31" s="2"/>
@@ -5477,11 +5476,11 @@
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E32:J32)&lt;2,"",MIN(1,(IF(ISNUMBER(E32),MIN(E32/2,1),0)+IF(ISNUMBER(F32),F32,0)+IF(ISNUMBER(G32),G32/100,0)+IF(ISNUMBER(H32),MIN(H32/10,1),0)+IF(ISNUMBER(J32),MIN(J32/50,1),0))/MAX(1,COUNT(E32:H32,J32))))</f>
         <v/>
       </c>
       <c r="L32" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K32="","",IF(K32&gt;=0.7,5,IF(K32&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M32" s="2"/>
@@ -5498,11 +5497,11 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(E33:J33)&lt;2,"",MIN(1,(IF(ISNUMBER(E33),MIN(E33/2,1),0)+IF(ISNUMBER(F33),F33,0)+IF(ISNUMBER(G33),G33/100,0)+IF(ISNUMBER(H33),MIN(H33/10,1),0)+IF(ISNUMBER(J33),MIN(J33/50,1),0))/MAX(1,COUNT(E33:H33,J33))))</f>
         <v/>
       </c>
       <c r="L33" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K33="","",IF(K33&gt;=0.7,5,IF(K33&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M33" s="2"/>
@@ -5530,8 +5529,8 @@
         <v>нет данных</v>
       </c>
       <c r="C37" t="str">
-        <f>IF(ISNUMBER(B37),IF(B37&gt;=0.7,"высокое",IF(B37&gt;=0.4,"среднее","низкое")),"нет данных")</f>
-        <v>нет данных</v>
+        <f>IF(ISNUMBER(B37),IF(B37&gt;=0.7,"высокое",IF(B37&gt;=0.4,"среднее","низкое")),"ДОСНЯТЬ")</f>
+        <v>ДОСНЯТЬ</v>
       </c>
       <c r="D37" t="s">
         <v>189</v>
@@ -5546,8 +5545,8 @@
         <v>нет данных</v>
       </c>
       <c r="C38" t="str">
-        <f>IF(ISNUMBER(B38),IF(B38&gt;=0.5,"высокая доля",IF(B38&gt;=0.25,"средняя доля","низкая доля")),"нет данных")</f>
-        <v>нет данных</v>
+        <f>IF(ISNUMBER(B38),IF(B38&gt;=0.5,"высокая доля",IF(B38&gt;=0.25,"средняя доля","низкая доля")),"ДОСНЯТЬ")</f>
+        <v>ДОСНЯТЬ</v>
       </c>
       <c r="D38" t="s">
         <v>191</v>
@@ -5558,7 +5557,7 @@
         <v>192</v>
       </c>
       <c r="D39" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -5605,40 +5604,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
     </row>
     <row r="2" spans="1:14" ht="16.05" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
     </row>
     <row r="3" spans="1:14" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -5699,20 +5698,20 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="9" t="str">
-        <f t="shared" ref="L4:L33" si="0">IF(COUNT(B4:K4)=0,"",MIN(1,(IF(COUNT(B4,D4,F4,H4)&gt;0,AVERAGE(B4,D4,F4,H4)/5,0)+IF(COUNT(C4,E4,G4,I4)&gt;0,MIN(SUM(C4,E4,G4,I4)/300,1),0)+IF(ISNUMBER(J4),MIN(J4/30,1),0)+IF(ISNUMBER(K4),MIN(K4/10,1),0))/MAX(1,(COUNT(B4,D4,F4,H4)&gt;0)+(COUNT(C4,E4,G4,I4)&gt;0)+ISNUMBER(J4)+ISNUMBER(K4))))</f>
+        <f>IF(COUNT(B4:K4)=0,"",MIN(1,(IF(COUNT(B4,D4,F4,H4)&gt;0,AVERAGE(B4,D4,F4,H4)/5,0)+IF(COUNT(C4,E4,G4,I4)&gt;0,MIN(SUM(C4,E4,G4,I4)/300,1),0)+IF(ISNUMBER(J4),MIN(J4/30,1),0)+IF(ISNUMBER(K4),MIN(K4/10,1),0))/MAX(1,(COUNT(B4,D4,F4,H4)&gt;0)+(COUNT(C4,E4,G4,I4)&gt;0)+ISNUMBER(J4)+ISNUMBER(K4))))</f>
         <v/>
       </c>
       <c r="M4" s="18" t="str">
-        <f t="shared" ref="M4:M33" si="1">IF(L4="","",IF(L4&gt;=0.7,5,IF(L4&gt;=0.4,3,1)))</f>
+        <f>IF(L4="","",IF(L4&gt;=0.7,5,IF(L4&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N4" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27">
       <c r="A5" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="10">
@@ -5729,20 +5728,20 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B5:K5)=0,"",MIN(1,(IF(COUNT(B5,D5,F5,H5)&gt;0,AVERAGE(B5,D5,F5,H5)/5,0)+IF(COUNT(C5,E5,G5,I5)&gt;0,MIN(SUM(C5,E5,G5,I5)/300,1),0)+IF(ISNUMBER(J5),MIN(J5/30,1),0)+IF(ISNUMBER(K5),MIN(K5/10,1),0))/MAX(1,(COUNT(B5,D5,F5,H5)&gt;0)+(COUNT(C5,E5,G5,I5)&gt;0)+ISNUMBER(J5)+ISNUMBER(K5))))</f>
         <v>0</v>
       </c>
       <c r="M5" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(L5="","",IF(L5&gt;=0.7,5,IF(L5&gt;=0.4,3,1)))</f>
         <v>1</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B6" s="19">
         <v>4.9000000000000004</v>
@@ -5759,20 +5758,20 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B6:K6)=0,"",MIN(1,(IF(COUNT(B6,D6,F6,H6)&gt;0,AVERAGE(B6,D6,F6,H6)/5,0)+IF(COUNT(C6,E6,G6,I6)&gt;0,MIN(SUM(C6,E6,G6,I6)/300,1),0)+IF(ISNUMBER(J6),MIN(J6/30,1),0)+IF(ISNUMBER(K6),MIN(K6/10,1),0))/MAX(1,(COUNT(B6,D6,F6,H6)&gt;0)+(COUNT(C6,E6,G6,I6)&gt;0)+ISNUMBER(J6)+ISNUMBER(K6))))</f>
         <v>0.53</v>
       </c>
       <c r="M6" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(L6="","",IF(L6&gt;=0.7,5,IF(L6&gt;=0.4,3,1)))</f>
         <v>3</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="27">
       <c r="A7" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="10"/>
@@ -5785,20 +5784,20 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B7:K7)=0,"",MIN(1,(IF(COUNT(B7,D7,F7,H7)&gt;0,AVERAGE(B7,D7,F7,H7)/5,0)+IF(COUNT(C7,E7,G7,I7)&gt;0,MIN(SUM(C7,E7,G7,I7)/300,1),0)+IF(ISNUMBER(J7),MIN(J7/30,1),0)+IF(ISNUMBER(K7),MIN(K7/10,1),0))/MAX(1,(COUNT(B7,D7,F7,H7)&gt;0)+(COUNT(C7,E7,G7,I7)&gt;0)+ISNUMBER(J7)+ISNUMBER(K7))))</f>
         <v/>
       </c>
       <c r="M7" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L7="","",IF(L7&gt;=0.7,5,IF(L7&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N7" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="54">
       <c r="A8" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="10"/>
@@ -5811,20 +5810,20 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B8:K8)=0,"",MIN(1,(IF(COUNT(B8,D8,F8,H8)&gt;0,AVERAGE(B8,D8,F8,H8)/5,0)+IF(COUNT(C8,E8,G8,I8)&gt;0,MIN(SUM(C8,E8,G8,I8)/300,1),0)+IF(ISNUMBER(J8),MIN(J8/30,1),0)+IF(ISNUMBER(K8),MIN(K8/10,1),0))/MAX(1,(COUNT(B8,D8,F8,H8)&gt;0)+(COUNT(C8,E8,G8,I8)&gt;0)+ISNUMBER(J8)+ISNUMBER(K8))))</f>
         <v/>
       </c>
       <c r="M8" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L8="","",IF(L8&gt;=0.7,5,IF(L8&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N8" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B9" s="19">
         <v>4</v>
@@ -5841,20 +5840,20 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B9:K9)=0,"",MIN(1,(IF(COUNT(B9,D9,F9,H9)&gt;0,AVERAGE(B9,D9,F9,H9)/5,0)+IF(COUNT(C9,E9,G9,I9)&gt;0,MIN(SUM(C9,E9,G9,I9)/300,1),0)+IF(ISNUMBER(J9),MIN(J9/30,1),0)+IF(ISNUMBER(K9),MIN(K9/10,1),0))/MAX(1,(COUNT(B9,D9,F9,H9)&gt;0)+(COUNT(C9,E9,G9,I9)&gt;0)+ISNUMBER(J9)+ISNUMBER(K9))))</f>
         <v>0.40166666666666667</v>
       </c>
       <c r="M9" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(L9="","",IF(L9&gt;=0.7,5,IF(L9&gt;=0.4,3,1)))</f>
         <v>3</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B10" s="19">
         <v>4.5</v>
@@ -5871,20 +5870,20 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B10:K10)=0,"",MIN(1,(IF(COUNT(B10,D10,F10,H10)&gt;0,AVERAGE(B10,D10,F10,H10)/5,0)+IF(COUNT(C10,E10,G10,I10)&gt;0,MIN(SUM(C10,E10,G10,I10)/300,1),0)+IF(ISNUMBER(J10),MIN(J10/30,1),0)+IF(ISNUMBER(K10),MIN(K10/10,1),0))/MAX(1,(COUNT(B10,D10,F10,H10)&gt;0)+(COUNT(C10,E10,G10,I10)&gt;0)+ISNUMBER(J10)+ISNUMBER(K10))))</f>
         <v>0.6</v>
       </c>
       <c r="M10" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(L10="","",IF(L10&gt;=0.7,5,IF(L10&gt;=0.4,3,1)))</f>
         <v>3</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B11" s="19">
         <v>4.5</v>
@@ -5901,20 +5900,20 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B11:K11)=0,"",MIN(1,(IF(COUNT(B11,D11,F11,H11)&gt;0,AVERAGE(B11,D11,F11,H11)/5,0)+IF(COUNT(C11,E11,G11,I11)&gt;0,MIN(SUM(C11,E11,G11,I11)/300,1),0)+IF(ISNUMBER(J11),MIN(J11/30,1),0)+IF(ISNUMBER(K11),MIN(K11/10,1),0))/MAX(1,(COUNT(B11,D11,F11,H11)&gt;0)+(COUNT(C11,E11,G11,I11)&gt;0)+ISNUMBER(J11)+ISNUMBER(K11))))</f>
         <v>0.45166666666666666</v>
       </c>
       <c r="M11" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(L11="","",IF(L11&gt;=0.7,5,IF(L11&gt;=0.4,3,1)))</f>
         <v>3</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B12" s="19">
         <v>4.5999999999999996</v>
@@ -5931,20 +5930,20 @@
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B12:K12)=0,"",MIN(1,(IF(COUNT(B12,D12,F12,H12)&gt;0,AVERAGE(B12,D12,F12,H12)/5,0)+IF(COUNT(C12,E12,G12,I12)&gt;0,MIN(SUM(C12,E12,G12,I12)/300,1),0)+IF(ISNUMBER(J12),MIN(J12/30,1),0)+IF(ISNUMBER(K12),MIN(K12/10,1),0))/MAX(1,(COUNT(B12,D12,F12,H12)&gt;0)+(COUNT(C12,E12,G12,I12)&gt;0)+ISNUMBER(J12)+ISNUMBER(K12))))</f>
         <v>0.96</v>
       </c>
       <c r="M12" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(L12="","",IF(L12&gt;=0.7,5,IF(L12&gt;=0.4,3,1)))</f>
         <v>5</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B13" s="19">
         <v>4.5</v>
@@ -5961,20 +5960,20 @@
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B13:K13)=0,"",MIN(1,(IF(COUNT(B13,D13,F13,H13)&gt;0,AVERAGE(B13,D13,F13,H13)/5,0)+IF(COUNT(C13,E13,G13,I13)&gt;0,MIN(SUM(C13,E13,G13,I13)/300,1),0)+IF(ISNUMBER(J13),MIN(J13/30,1),0)+IF(ISNUMBER(K13),MIN(K13/10,1),0))/MAX(1,(COUNT(B13,D13,F13,H13)&gt;0)+(COUNT(C13,E13,G13,I13)&gt;0)+ISNUMBER(J13)+ISNUMBER(K13))))</f>
         <v>0.45666666666666667</v>
       </c>
       <c r="M13" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(L13="","",IF(L13&gt;=0.7,5,IF(L13&gt;=0.4,3,1)))</f>
         <v>3</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="10">
@@ -5989,20 +5988,20 @@
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B14:K14)=0,"",MIN(1,(IF(COUNT(B14,D14,F14,H14)&gt;0,AVERAGE(B14,D14,F14,H14)/5,0)+IF(COUNT(C14,E14,G14,I14)&gt;0,MIN(SUM(C14,E14,G14,I14)/300,1),0)+IF(ISNUMBER(J14),MIN(J14/30,1),0)+IF(ISNUMBER(K14),MIN(K14/10,1),0))/MAX(1,(COUNT(B14,D14,F14,H14)&gt;0)+(COUNT(C14,E14,G14,I14)&gt;0)+ISNUMBER(J14)+ISNUMBER(K14))))</f>
         <v>0</v>
       </c>
       <c r="M14" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(L14="","",IF(L14&gt;=0.7,5,IF(L14&gt;=0.4,3,1)))</f>
         <v>1</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="27">
       <c r="A15" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B15" s="19">
         <v>4.7</v>
@@ -6019,15 +6018,15 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B15:K15)=0,"",MIN(1,(IF(COUNT(B15,D15,F15,H15)&gt;0,AVERAGE(B15,D15,F15,H15)/5,0)+IF(COUNT(C15,E15,G15,I15)&gt;0,MIN(SUM(C15,E15,G15,I15)/300,1),0)+IF(ISNUMBER(J15),MIN(J15/30,1),0)+IF(ISNUMBER(K15),MIN(K15/10,1),0))/MAX(1,(COUNT(B15,D15,F15,H15)&gt;0)+(COUNT(C15,E15,G15,I15)&gt;0)+ISNUMBER(J15)+ISNUMBER(K15))))</f>
         <v>0.50166666666666671</v>
       </c>
       <c r="M15" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(L15="","",IF(L15&gt;=0.7,5,IF(L15&gt;=0.4,3,1)))</f>
         <v>3</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -6043,11 +6042,11 @@
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B16:K16)=0,"",MIN(1,(IF(COUNT(B16,D16,F16,H16)&gt;0,AVERAGE(B16,D16,F16,H16)/5,0)+IF(COUNT(C16,E16,G16,I16)&gt;0,MIN(SUM(C16,E16,G16,I16)/300,1),0)+IF(ISNUMBER(J16),MIN(J16/30,1),0)+IF(ISNUMBER(K16),MIN(K16/10,1),0))/MAX(1,(COUNT(B16,D16,F16,H16)&gt;0)+(COUNT(C16,E16,G16,I16)&gt;0)+ISNUMBER(J16)+ISNUMBER(K16))))</f>
         <v/>
       </c>
       <c r="M16" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L16="","",IF(L16&gt;=0.7,5,IF(L16&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N16" s="2"/>
@@ -6065,11 +6064,11 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B17:K17)=0,"",MIN(1,(IF(COUNT(B17,D17,F17,H17)&gt;0,AVERAGE(B17,D17,F17,H17)/5,0)+IF(COUNT(C17,E17,G17,I17)&gt;0,MIN(SUM(C17,E17,G17,I17)/300,1),0)+IF(ISNUMBER(J17),MIN(J17/30,1),0)+IF(ISNUMBER(K17),MIN(K17/10,1),0))/MAX(1,(COUNT(B17,D17,F17,H17)&gt;0)+(COUNT(C17,E17,G17,I17)&gt;0)+ISNUMBER(J17)+ISNUMBER(K17))))</f>
         <v/>
       </c>
       <c r="M17" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L17="","",IF(L17&gt;=0.7,5,IF(L17&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N17" s="2"/>
@@ -6087,11 +6086,11 @@
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B18:K18)=0,"",MIN(1,(IF(COUNT(B18,D18,F18,H18)&gt;0,AVERAGE(B18,D18,F18,H18)/5,0)+IF(COUNT(C18,E18,G18,I18)&gt;0,MIN(SUM(C18,E18,G18,I18)/300,1),0)+IF(ISNUMBER(J18),MIN(J18/30,1),0)+IF(ISNUMBER(K18),MIN(K18/10,1),0))/MAX(1,(COUNT(B18,D18,F18,H18)&gt;0)+(COUNT(C18,E18,G18,I18)&gt;0)+ISNUMBER(J18)+ISNUMBER(K18))))</f>
         <v/>
       </c>
       <c r="M18" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L18="","",IF(L18&gt;=0.7,5,IF(L18&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N18" s="2"/>
@@ -6109,11 +6108,11 @@
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B19:K19)=0,"",MIN(1,(IF(COUNT(B19,D19,F19,H19)&gt;0,AVERAGE(B19,D19,F19,H19)/5,0)+IF(COUNT(C19,E19,G19,I19)&gt;0,MIN(SUM(C19,E19,G19,I19)/300,1),0)+IF(ISNUMBER(J19),MIN(J19/30,1),0)+IF(ISNUMBER(K19),MIN(K19/10,1),0))/MAX(1,(COUNT(B19,D19,F19,H19)&gt;0)+(COUNT(C19,E19,G19,I19)&gt;0)+ISNUMBER(J19)+ISNUMBER(K19))))</f>
         <v/>
       </c>
       <c r="M19" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L19="","",IF(L19&gt;=0.7,5,IF(L19&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N19" s="2"/>
@@ -6131,11 +6130,11 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B20:K20)=0,"",MIN(1,(IF(COUNT(B20,D20,F20,H20)&gt;0,AVERAGE(B20,D20,F20,H20)/5,0)+IF(COUNT(C20,E20,G20,I20)&gt;0,MIN(SUM(C20,E20,G20,I20)/300,1),0)+IF(ISNUMBER(J20),MIN(J20/30,1),0)+IF(ISNUMBER(K20),MIN(K20/10,1),0))/MAX(1,(COUNT(B20,D20,F20,H20)&gt;0)+(COUNT(C20,E20,G20,I20)&gt;0)+ISNUMBER(J20)+ISNUMBER(K20))))</f>
         <v/>
       </c>
       <c r="M20" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L20="","",IF(L20&gt;=0.7,5,IF(L20&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N20" s="2"/>
@@ -6153,11 +6152,11 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B21:K21)=0,"",MIN(1,(IF(COUNT(B21,D21,F21,H21)&gt;0,AVERAGE(B21,D21,F21,H21)/5,0)+IF(COUNT(C21,E21,G21,I21)&gt;0,MIN(SUM(C21,E21,G21,I21)/300,1),0)+IF(ISNUMBER(J21),MIN(J21/30,1),0)+IF(ISNUMBER(K21),MIN(K21/10,1),0))/MAX(1,(COUNT(B21,D21,F21,H21)&gt;0)+(COUNT(C21,E21,G21,I21)&gt;0)+ISNUMBER(J21)+ISNUMBER(K21))))</f>
         <v/>
       </c>
       <c r="M21" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L21="","",IF(L21&gt;=0.7,5,IF(L21&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N21" s="2"/>
@@ -6175,11 +6174,11 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B22:K22)=0,"",MIN(1,(IF(COUNT(B22,D22,F22,H22)&gt;0,AVERAGE(B22,D22,F22,H22)/5,0)+IF(COUNT(C22,E22,G22,I22)&gt;0,MIN(SUM(C22,E22,G22,I22)/300,1),0)+IF(ISNUMBER(J22),MIN(J22/30,1),0)+IF(ISNUMBER(K22),MIN(K22/10,1),0))/MAX(1,(COUNT(B22,D22,F22,H22)&gt;0)+(COUNT(C22,E22,G22,I22)&gt;0)+ISNUMBER(J22)+ISNUMBER(K22))))</f>
         <v/>
       </c>
       <c r="M22" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L22="","",IF(L22&gt;=0.7,5,IF(L22&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N22" s="2"/>
@@ -6197,11 +6196,11 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B23:K23)=0,"",MIN(1,(IF(COUNT(B23,D23,F23,H23)&gt;0,AVERAGE(B23,D23,F23,H23)/5,0)+IF(COUNT(C23,E23,G23,I23)&gt;0,MIN(SUM(C23,E23,G23,I23)/300,1),0)+IF(ISNUMBER(J23),MIN(J23/30,1),0)+IF(ISNUMBER(K23),MIN(K23/10,1),0))/MAX(1,(COUNT(B23,D23,F23,H23)&gt;0)+(COUNT(C23,E23,G23,I23)&gt;0)+ISNUMBER(J23)+ISNUMBER(K23))))</f>
         <v/>
       </c>
       <c r="M23" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L23="","",IF(L23&gt;=0.7,5,IF(L23&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N23" s="2"/>
@@ -6219,11 +6218,11 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B24:K24)=0,"",MIN(1,(IF(COUNT(B24,D24,F24,H24)&gt;0,AVERAGE(B24,D24,F24,H24)/5,0)+IF(COUNT(C24,E24,G24,I24)&gt;0,MIN(SUM(C24,E24,G24,I24)/300,1),0)+IF(ISNUMBER(J24),MIN(J24/30,1),0)+IF(ISNUMBER(K24),MIN(K24/10,1),0))/MAX(1,(COUNT(B24,D24,F24,H24)&gt;0)+(COUNT(C24,E24,G24,I24)&gt;0)+ISNUMBER(J24)+ISNUMBER(K24))))</f>
         <v/>
       </c>
       <c r="M24" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L24="","",IF(L24&gt;=0.7,5,IF(L24&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N24" s="2"/>
@@ -6241,11 +6240,11 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B25:K25)=0,"",MIN(1,(IF(COUNT(B25,D25,F25,H25)&gt;0,AVERAGE(B25,D25,F25,H25)/5,0)+IF(COUNT(C25,E25,G25,I25)&gt;0,MIN(SUM(C25,E25,G25,I25)/300,1),0)+IF(ISNUMBER(J25),MIN(J25/30,1),0)+IF(ISNUMBER(K25),MIN(K25/10,1),0))/MAX(1,(COUNT(B25,D25,F25,H25)&gt;0)+(COUNT(C25,E25,G25,I25)&gt;0)+ISNUMBER(J25)+ISNUMBER(K25))))</f>
         <v/>
       </c>
       <c r="M25" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L25="","",IF(L25&gt;=0.7,5,IF(L25&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N25" s="2"/>
@@ -6263,11 +6262,11 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B26:K26)=0,"",MIN(1,(IF(COUNT(B26,D26,F26,H26)&gt;0,AVERAGE(B26,D26,F26,H26)/5,0)+IF(COUNT(C26,E26,G26,I26)&gt;0,MIN(SUM(C26,E26,G26,I26)/300,1),0)+IF(ISNUMBER(J26),MIN(J26/30,1),0)+IF(ISNUMBER(K26),MIN(K26/10,1),0))/MAX(1,(COUNT(B26,D26,F26,H26)&gt;0)+(COUNT(C26,E26,G26,I26)&gt;0)+ISNUMBER(J26)+ISNUMBER(K26))))</f>
         <v/>
       </c>
       <c r="M26" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L26="","",IF(L26&gt;=0.7,5,IF(L26&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N26" s="2"/>
@@ -6285,11 +6284,11 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B27:K27)=0,"",MIN(1,(IF(COUNT(B27,D27,F27,H27)&gt;0,AVERAGE(B27,D27,F27,H27)/5,0)+IF(COUNT(C27,E27,G27,I27)&gt;0,MIN(SUM(C27,E27,G27,I27)/300,1),0)+IF(ISNUMBER(J27),MIN(J27/30,1),0)+IF(ISNUMBER(K27),MIN(K27/10,1),0))/MAX(1,(COUNT(B27,D27,F27,H27)&gt;0)+(COUNT(C27,E27,G27,I27)&gt;0)+ISNUMBER(J27)+ISNUMBER(K27))))</f>
         <v/>
       </c>
       <c r="M27" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L27="","",IF(L27&gt;=0.7,5,IF(L27&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N27" s="2"/>
@@ -6307,11 +6306,11 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B28:K28)=0,"",MIN(1,(IF(COUNT(B28,D28,F28,H28)&gt;0,AVERAGE(B28,D28,F28,H28)/5,0)+IF(COUNT(C28,E28,G28,I28)&gt;0,MIN(SUM(C28,E28,G28,I28)/300,1),0)+IF(ISNUMBER(J28),MIN(J28/30,1),0)+IF(ISNUMBER(K28),MIN(K28/10,1),0))/MAX(1,(COUNT(B28,D28,F28,H28)&gt;0)+(COUNT(C28,E28,G28,I28)&gt;0)+ISNUMBER(J28)+ISNUMBER(K28))))</f>
         <v/>
       </c>
       <c r="M28" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L28="","",IF(L28&gt;=0.7,5,IF(L28&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N28" s="2"/>
@@ -6329,11 +6328,11 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B29:K29)=0,"",MIN(1,(IF(COUNT(B29,D29,F29,H29)&gt;0,AVERAGE(B29,D29,F29,H29)/5,0)+IF(COUNT(C29,E29,G29,I29)&gt;0,MIN(SUM(C29,E29,G29,I29)/300,1),0)+IF(ISNUMBER(J29),MIN(J29/30,1),0)+IF(ISNUMBER(K29),MIN(K29/10,1),0))/MAX(1,(COUNT(B29,D29,F29,H29)&gt;0)+(COUNT(C29,E29,G29,I29)&gt;0)+ISNUMBER(J29)+ISNUMBER(K29))))</f>
         <v/>
       </c>
       <c r="M29" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L29="","",IF(L29&gt;=0.7,5,IF(L29&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N29" s="2"/>
@@ -6351,11 +6350,11 @@
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B30:K30)=0,"",MIN(1,(IF(COUNT(B30,D30,F30,H30)&gt;0,AVERAGE(B30,D30,F30,H30)/5,0)+IF(COUNT(C30,E30,G30,I30)&gt;0,MIN(SUM(C30,E30,G30,I30)/300,1),0)+IF(ISNUMBER(J30),MIN(J30/30,1),0)+IF(ISNUMBER(K30),MIN(K30/10,1),0))/MAX(1,(COUNT(B30,D30,F30,H30)&gt;0)+(COUNT(C30,E30,G30,I30)&gt;0)+ISNUMBER(J30)+ISNUMBER(K30))))</f>
         <v/>
       </c>
       <c r="M30" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L30="","",IF(L30&gt;=0.7,5,IF(L30&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N30" s="2"/>
@@ -6373,11 +6372,11 @@
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B31:K31)=0,"",MIN(1,(IF(COUNT(B31,D31,F31,H31)&gt;0,AVERAGE(B31,D31,F31,H31)/5,0)+IF(COUNT(C31,E31,G31,I31)&gt;0,MIN(SUM(C31,E31,G31,I31)/300,1),0)+IF(ISNUMBER(J31),MIN(J31/30,1),0)+IF(ISNUMBER(K31),MIN(K31/10,1),0))/MAX(1,(COUNT(B31,D31,F31,H31)&gt;0)+(COUNT(C31,E31,G31,I31)&gt;0)+ISNUMBER(J31)+ISNUMBER(K31))))</f>
         <v/>
       </c>
       <c r="M31" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L31="","",IF(L31&gt;=0.7,5,IF(L31&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N31" s="2"/>
@@ -6395,11 +6394,11 @@
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B32:K32)=0,"",MIN(1,(IF(COUNT(B32,D32,F32,H32)&gt;0,AVERAGE(B32,D32,F32,H32)/5,0)+IF(COUNT(C32,E32,G32,I32)&gt;0,MIN(SUM(C32,E32,G32,I32)/300,1),0)+IF(ISNUMBER(J32),MIN(J32/30,1),0)+IF(ISNUMBER(K32),MIN(K32/10,1),0))/MAX(1,(COUNT(B32,D32,F32,H32)&gt;0)+(COUNT(C32,E32,G32,I32)&gt;0)+ISNUMBER(J32)+ISNUMBER(K32))))</f>
         <v/>
       </c>
       <c r="M32" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L32="","",IF(L32&gt;=0.7,5,IF(L32&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N32" s="2"/>
@@ -6417,11 +6416,11 @@
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNT(B33:K33)=0,"",MIN(1,(IF(COUNT(B33,D33,F33,H33)&gt;0,AVERAGE(B33,D33,F33,H33)/5,0)+IF(COUNT(C33,E33,G33,I33)&gt;0,MIN(SUM(C33,E33,G33,I33)/300,1),0)+IF(ISNUMBER(J33),MIN(J33/30,1),0)+IF(ISNUMBER(K33),MIN(K33/10,1),0))/MAX(1,(COUNT(B33,D33,F33,H33)&gt;0)+(COUNT(C33,E33,G33,I33)&gt;0)+ISNUMBER(J33)+ISNUMBER(K33))))</f>
         <v/>
       </c>
       <c r="M33" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(L33="","",IF(L33&gt;=0.7,5,IF(L33&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="N33" s="2"/>
@@ -6469,7 +6468,7 @@
         <v>низкий барьер</v>
       </c>
       <c r="D38" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -6514,38 +6513,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
     </row>
     <row r="2" spans="1:13" ht="16.05" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
     </row>
     <row r="3" spans="1:13" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -6588,7 +6587,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54">
+    <row r="4" spans="1:13" ht="67.5">
       <c r="A4" s="4" t="s">
         <v>395</v>
       </c>
@@ -6606,20 +6605,20 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="9">
-        <f t="shared" ref="K4:K33" si="0">IF(COUNTA(B4:J4)=0,"",MIN(1,(IF(ISNUMBER(B4),MIN(B4/500000,1),0)+IF(ISNUMBER(C4),MIN(C4/60,1),0)+IF(ISNUMBER(D4),D4/5,0)+IF(ISNUMBER(E4),E4/5,0)+IF(F4="да",1,0)+IF(G4="да",1,0)+IF(ISNUMBER(H4),MIN(H4/50,1),0)+IF(ISNUMBER(I4),MIN(I4/6,1),0)+IF(ISNUMBER(J4),IF(J4&gt;0,1,0),0))/MAX(1,ISNUMBER(B4)+ISNUMBER(C4)+ISNUMBER(D4)+ISNUMBER(E4)+(F4&lt;&gt;"")+(G4&lt;&gt;"")+ISNUMBER(H4)+ISNUMBER(I4)+ISNUMBER(J4))))</f>
+        <f>IF(COUNTA(B4:J4)=0,"",MIN(1,(IF(ISNUMBER(B4),MIN(B4/500000,1),0)+IF(ISNUMBER(C4),MIN(C4/60,1),0)+IF(ISNUMBER(D4),D4/5,0)+IF(ISNUMBER(E4),E4/5,0)+IF(F4="да",1,0)+IF(G4="да",1,0)+IF(ISNUMBER(H4),MIN(H4/50,1),0)+IF(ISNUMBER(I4),MIN(I4/6,1),0)+IF(ISNUMBER(J4),IF(J4&gt;0,1,0),0))/MAX(1,ISNUMBER(B4)+ISNUMBER(C4)+ISNUMBER(D4)+ISNUMBER(E4)+(F4&lt;&gt;"")+(G4&lt;&gt;"")+ISNUMBER(H4)+ISNUMBER(I4)+ISNUMBER(J4))))</f>
         <v>1</v>
       </c>
       <c r="L4" s="18">
-        <f t="shared" ref="L4:L33" si="1">IF(K4="","",IF(K4&gt;=0.7,5,IF(K4&gt;=0.4,3,1)))</f>
+        <f>IF(K4="","",IF(K4&gt;=0.7,5,IF(K4&gt;=0.4,3,1)))</f>
         <v>5</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="54">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="67.5">
       <c r="A5" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="17"/>
@@ -6635,20 +6634,20 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B5:J5)=0,"",MIN(1,(IF(ISNUMBER(B5),MIN(B5/500000,1),0)+IF(ISNUMBER(C5),MIN(C5/60,1),0)+IF(ISNUMBER(D5),D5/5,0)+IF(ISNUMBER(E5),E5/5,0)+IF(F5="да",1,0)+IF(G5="да",1,0)+IF(ISNUMBER(H5),MIN(H5/50,1),0)+IF(ISNUMBER(I5),MIN(I5/6,1),0)+IF(ISNUMBER(J5),IF(J5&gt;0,1,0),0))/MAX(1,ISNUMBER(B5)+ISNUMBER(C5)+ISNUMBER(D5)+ISNUMBER(E5)+(F5&lt;&gt;"")+(G5&lt;&gt;"")+ISNUMBER(H5)+ISNUMBER(I5)+ISNUMBER(J5))))</f>
         <v>0.6</v>
       </c>
       <c r="L5" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(K5="","",IF(K5&gt;=0.7,5,IF(K5&gt;=0.4,3,1)))</f>
         <v>3</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="54">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="67.5">
       <c r="A6" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="17"/>
@@ -6664,20 +6663,20 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B6:J6)=0,"",MIN(1,(IF(ISNUMBER(B6),MIN(B6/500000,1),0)+IF(ISNUMBER(C6),MIN(C6/60,1),0)+IF(ISNUMBER(D6),D6/5,0)+IF(ISNUMBER(E6),E6/5,0)+IF(F6="да",1,0)+IF(G6="да",1,0)+IF(ISNUMBER(H6),MIN(H6/50,1),0)+IF(ISNUMBER(I6),MIN(I6/6,1),0)+IF(ISNUMBER(J6),IF(J6&gt;0,1,0),0))/MAX(1,ISNUMBER(B6)+ISNUMBER(C6)+ISNUMBER(D6)+ISNUMBER(E6)+(F6&lt;&gt;"")+(G6&lt;&gt;"")+ISNUMBER(H6)+ISNUMBER(I6)+ISNUMBER(J6))))</f>
         <v>0.9</v>
       </c>
       <c r="L6" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(K6="","",IF(K6&gt;=0.7,5,IF(K6&gt;=0.4,3,1)))</f>
         <v>5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="54">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="67.5">
       <c r="A7" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="17"/>
@@ -6693,20 +6692,20 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B7:J7)=0,"",MIN(1,(IF(ISNUMBER(B7),MIN(B7/500000,1),0)+IF(ISNUMBER(C7),MIN(C7/60,1),0)+IF(ISNUMBER(D7),D7/5,0)+IF(ISNUMBER(E7),E7/5,0)+IF(F7="да",1,0)+IF(G7="да",1,0)+IF(ISNUMBER(H7),MIN(H7/50,1),0)+IF(ISNUMBER(I7),MIN(I7/6,1),0)+IF(ISNUMBER(J7),IF(J7&gt;0,1,0),0))/MAX(1,ISNUMBER(B7)+ISNUMBER(C7)+ISNUMBER(D7)+ISNUMBER(E7)+(F7&lt;&gt;"")+(G7&lt;&gt;"")+ISNUMBER(H7)+ISNUMBER(I7)+ISNUMBER(J7))))</f>
         <v>0.8</v>
       </c>
       <c r="L7" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(K7="","",IF(K7&gt;=0.7,5,IF(K7&gt;=0.4,3,1)))</f>
         <v>5</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="54">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="67.5">
       <c r="A8" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="17"/>
@@ -6722,20 +6721,20 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B8:J8)=0,"",MIN(1,(IF(ISNUMBER(B8),MIN(B8/500000,1),0)+IF(ISNUMBER(C8),MIN(C8/60,1),0)+IF(ISNUMBER(D8),D8/5,0)+IF(ISNUMBER(E8),E8/5,0)+IF(F8="да",1,0)+IF(G8="да",1,0)+IF(ISNUMBER(H8),MIN(H8/50,1),0)+IF(ISNUMBER(I8),MIN(I8/6,1),0)+IF(ISNUMBER(J8),IF(J8&gt;0,1,0),0))/MAX(1,ISNUMBER(B8)+ISNUMBER(C8)+ISNUMBER(D8)+ISNUMBER(E8)+(F8&lt;&gt;"")+(G8&lt;&gt;"")+ISNUMBER(H8)+ISNUMBER(I8)+ISNUMBER(J8))))</f>
         <v>0.5</v>
       </c>
       <c r="L8" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(K8="","",IF(K8&gt;=0.7,5,IF(K8&gt;=0.4,3,1)))</f>
         <v>3</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="54">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="67.5">
       <c r="A9" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="17"/>
@@ -6751,20 +6750,20 @@
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B9:J9)=0,"",MIN(1,(IF(ISNUMBER(B9),MIN(B9/500000,1),0)+IF(ISNUMBER(C9),MIN(C9/60,1),0)+IF(ISNUMBER(D9),D9/5,0)+IF(ISNUMBER(E9),E9/5,0)+IF(F9="да",1,0)+IF(G9="да",1,0)+IF(ISNUMBER(H9),MIN(H9/50,1),0)+IF(ISNUMBER(I9),MIN(I9/6,1),0)+IF(ISNUMBER(J9),IF(J9&gt;0,1,0),0))/MAX(1,ISNUMBER(B9)+ISNUMBER(C9)+ISNUMBER(D9)+ISNUMBER(E9)+(F9&lt;&gt;"")+(G9&lt;&gt;"")+ISNUMBER(H9)+ISNUMBER(I9)+ISNUMBER(J9))))</f>
         <v>0.4</v>
       </c>
       <c r="L9" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(K9="","",IF(K9&gt;=0.7,5,IF(K9&gt;=0.4,3,1)))</f>
         <v>3</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="54">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="67.5">
       <c r="A10" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="17"/>
@@ -6780,20 +6779,20 @@
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B10:J10)=0,"",MIN(1,(IF(ISNUMBER(B10),MIN(B10/500000,1),0)+IF(ISNUMBER(C10),MIN(C10/60,1),0)+IF(ISNUMBER(D10),D10/5,0)+IF(ISNUMBER(E10),E10/5,0)+IF(F10="да",1,0)+IF(G10="да",1,0)+IF(ISNUMBER(H10),MIN(H10/50,1),0)+IF(ISNUMBER(I10),MIN(I10/6,1),0)+IF(ISNUMBER(J10),IF(J10&gt;0,1,0),0))/MAX(1,ISNUMBER(B10)+ISNUMBER(C10)+ISNUMBER(D10)+ISNUMBER(E10)+(F10&lt;&gt;"")+(G10&lt;&gt;"")+ISNUMBER(H10)+ISNUMBER(I10)+ISNUMBER(J10))))</f>
         <v>0.6</v>
       </c>
       <c r="L10" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(K10="","",IF(K10&gt;=0.7,5,IF(K10&gt;=0.4,3,1)))</f>
         <v>3</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="54">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="67.5">
       <c r="A11" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="17"/>
@@ -6809,20 +6808,20 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B11:J11)=0,"",MIN(1,(IF(ISNUMBER(B11),MIN(B11/500000,1),0)+IF(ISNUMBER(C11),MIN(C11/60,1),0)+IF(ISNUMBER(D11),D11/5,0)+IF(ISNUMBER(E11),E11/5,0)+IF(F11="да",1,0)+IF(G11="да",1,0)+IF(ISNUMBER(H11),MIN(H11/50,1),0)+IF(ISNUMBER(I11),MIN(I11/6,1),0)+IF(ISNUMBER(J11),IF(J11&gt;0,1,0),0))/MAX(1,ISNUMBER(B11)+ISNUMBER(C11)+ISNUMBER(D11)+ISNUMBER(E11)+(F11&lt;&gt;"")+(G11&lt;&gt;"")+ISNUMBER(H11)+ISNUMBER(I11)+ISNUMBER(J11))))</f>
         <v>0.6</v>
       </c>
       <c r="L11" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(K11="","",IF(K11&gt;=0.7,5,IF(K11&gt;=0.4,3,1)))</f>
         <v>3</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="54">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="67.5">
       <c r="A12" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="17"/>
@@ -6838,20 +6837,20 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B12:J12)=0,"",MIN(1,(IF(ISNUMBER(B12),MIN(B12/500000,1),0)+IF(ISNUMBER(C12),MIN(C12/60,1),0)+IF(ISNUMBER(D12),D12/5,0)+IF(ISNUMBER(E12),E12/5,0)+IF(F12="да",1,0)+IF(G12="да",1,0)+IF(ISNUMBER(H12),MIN(H12/50,1),0)+IF(ISNUMBER(I12),MIN(I12/6,1),0)+IF(ISNUMBER(J12),IF(J12&gt;0,1,0),0))/MAX(1,ISNUMBER(B12)+ISNUMBER(C12)+ISNUMBER(D12)+ISNUMBER(E12)+(F12&lt;&gt;"")+(G12&lt;&gt;"")+ISNUMBER(H12)+ISNUMBER(I12)+ISNUMBER(J12))))</f>
         <v>1</v>
       </c>
       <c r="L12" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(K12="","",IF(K12&gt;=0.7,5,IF(K12&gt;=0.4,3,1)))</f>
         <v>5</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="54">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="67.5">
       <c r="A13" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="17"/>
@@ -6867,20 +6866,20 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B13:J13)=0,"",MIN(1,(IF(ISNUMBER(B13),MIN(B13/500000,1),0)+IF(ISNUMBER(C13),MIN(C13/60,1),0)+IF(ISNUMBER(D13),D13/5,0)+IF(ISNUMBER(E13),E13/5,0)+IF(F13="да",1,0)+IF(G13="да",1,0)+IF(ISNUMBER(H13),MIN(H13/50,1),0)+IF(ISNUMBER(I13),MIN(I13/6,1),0)+IF(ISNUMBER(J13),IF(J13&gt;0,1,0),0))/MAX(1,ISNUMBER(B13)+ISNUMBER(C13)+ISNUMBER(D13)+ISNUMBER(E13)+(F13&lt;&gt;"")+(G13&lt;&gt;"")+ISNUMBER(H13)+ISNUMBER(I13)+ISNUMBER(J13))))</f>
         <v>0.9</v>
       </c>
       <c r="L13" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(K13="","",IF(K13&gt;=0.7,5,IF(K13&gt;=0.4,3,1)))</f>
         <v>5</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="54">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="67.5">
       <c r="A14" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="17"/>
@@ -6896,20 +6895,20 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B14:J14)=0,"",MIN(1,(IF(ISNUMBER(B14),MIN(B14/500000,1),0)+IF(ISNUMBER(C14),MIN(C14/60,1),0)+IF(ISNUMBER(D14),D14/5,0)+IF(ISNUMBER(E14),E14/5,0)+IF(F14="да",1,0)+IF(G14="да",1,0)+IF(ISNUMBER(H14),MIN(H14/50,1),0)+IF(ISNUMBER(I14),MIN(I14/6,1),0)+IF(ISNUMBER(J14),IF(J14&gt;0,1,0),0))/MAX(1,ISNUMBER(B14)+ISNUMBER(C14)+ISNUMBER(D14)+ISNUMBER(E14)+(F14&lt;&gt;"")+(G14&lt;&gt;"")+ISNUMBER(H14)+ISNUMBER(I14)+ISNUMBER(J14))))</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="L14" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(K14="","",IF(K14&gt;=0.7,5,IF(K14&gt;=0.4,3,1)))</f>
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="54">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="67.5">
       <c r="A15" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="17"/>
@@ -6925,15 +6924,15 @@
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="9">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B15:J15)=0,"",MIN(1,(IF(ISNUMBER(B15),MIN(B15/500000,1),0)+IF(ISNUMBER(C15),MIN(C15/60,1),0)+IF(ISNUMBER(D15),D15/5,0)+IF(ISNUMBER(E15),E15/5,0)+IF(F15="да",1,0)+IF(G15="да",1,0)+IF(ISNUMBER(H15),MIN(H15/50,1),0)+IF(ISNUMBER(I15),MIN(I15/6,1),0)+IF(ISNUMBER(J15),IF(J15&gt;0,1,0),0))/MAX(1,ISNUMBER(B15)+ISNUMBER(C15)+ISNUMBER(D15)+ISNUMBER(E15)+(F15&lt;&gt;"")+(G15&lt;&gt;"")+ISNUMBER(H15)+ISNUMBER(I15)+ISNUMBER(J15))))</f>
         <v>0.8</v>
       </c>
       <c r="L15" s="18">
-        <f t="shared" si="1"/>
+        <f>IF(K15="","",IF(K15&gt;=0.7,5,IF(K15&gt;=0.4,3,1)))</f>
         <v>5</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -6948,11 +6947,11 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B16:J16)=0,"",MIN(1,(IF(ISNUMBER(B16),MIN(B16/500000,1),0)+IF(ISNUMBER(C16),MIN(C16/60,1),0)+IF(ISNUMBER(D16),D16/5,0)+IF(ISNUMBER(E16),E16/5,0)+IF(F16="да",1,0)+IF(G16="да",1,0)+IF(ISNUMBER(H16),MIN(H16/50,1),0)+IF(ISNUMBER(I16),MIN(I16/6,1),0)+IF(ISNUMBER(J16),IF(J16&gt;0,1,0),0))/MAX(1,ISNUMBER(B16)+ISNUMBER(C16)+ISNUMBER(D16)+ISNUMBER(E16)+(F16&lt;&gt;"")+(G16&lt;&gt;"")+ISNUMBER(H16)+ISNUMBER(I16)+ISNUMBER(J16))))</f>
         <v/>
       </c>
       <c r="L16" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K16="","",IF(K16&gt;=0.7,5,IF(K16&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M16" s="2"/>
@@ -6969,11 +6968,11 @@
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B17:J17)=0,"",MIN(1,(IF(ISNUMBER(B17),MIN(B17/500000,1),0)+IF(ISNUMBER(C17),MIN(C17/60,1),0)+IF(ISNUMBER(D17),D17/5,0)+IF(ISNUMBER(E17),E17/5,0)+IF(F17="да",1,0)+IF(G17="да",1,0)+IF(ISNUMBER(H17),MIN(H17/50,1),0)+IF(ISNUMBER(I17),MIN(I17/6,1),0)+IF(ISNUMBER(J17),IF(J17&gt;0,1,0),0))/MAX(1,ISNUMBER(B17)+ISNUMBER(C17)+ISNUMBER(D17)+ISNUMBER(E17)+(F17&lt;&gt;"")+(G17&lt;&gt;"")+ISNUMBER(H17)+ISNUMBER(I17)+ISNUMBER(J17))))</f>
         <v/>
       </c>
       <c r="L17" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K17="","",IF(K17&gt;=0.7,5,IF(K17&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M17" s="2"/>
@@ -6990,11 +6989,11 @@
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B18:J18)=0,"",MIN(1,(IF(ISNUMBER(B18),MIN(B18/500000,1),0)+IF(ISNUMBER(C18),MIN(C18/60,1),0)+IF(ISNUMBER(D18),D18/5,0)+IF(ISNUMBER(E18),E18/5,0)+IF(F18="да",1,0)+IF(G18="да",1,0)+IF(ISNUMBER(H18),MIN(H18/50,1),0)+IF(ISNUMBER(I18),MIN(I18/6,1),0)+IF(ISNUMBER(J18),IF(J18&gt;0,1,0),0))/MAX(1,ISNUMBER(B18)+ISNUMBER(C18)+ISNUMBER(D18)+ISNUMBER(E18)+(F18&lt;&gt;"")+(G18&lt;&gt;"")+ISNUMBER(H18)+ISNUMBER(I18)+ISNUMBER(J18))))</f>
         <v/>
       </c>
       <c r="L18" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K18="","",IF(K18&gt;=0.7,5,IF(K18&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M18" s="2"/>
@@ -7011,11 +7010,11 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B19:J19)=0,"",MIN(1,(IF(ISNUMBER(B19),MIN(B19/500000,1),0)+IF(ISNUMBER(C19),MIN(C19/60,1),0)+IF(ISNUMBER(D19),D19/5,0)+IF(ISNUMBER(E19),E19/5,0)+IF(F19="да",1,0)+IF(G19="да",1,0)+IF(ISNUMBER(H19),MIN(H19/50,1),0)+IF(ISNUMBER(I19),MIN(I19/6,1),0)+IF(ISNUMBER(J19),IF(J19&gt;0,1,0),0))/MAX(1,ISNUMBER(B19)+ISNUMBER(C19)+ISNUMBER(D19)+ISNUMBER(E19)+(F19&lt;&gt;"")+(G19&lt;&gt;"")+ISNUMBER(H19)+ISNUMBER(I19)+ISNUMBER(J19))))</f>
         <v/>
       </c>
       <c r="L19" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K19="","",IF(K19&gt;=0.7,5,IF(K19&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M19" s="2"/>
@@ -7032,11 +7031,11 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B20:J20)=0,"",MIN(1,(IF(ISNUMBER(B20),MIN(B20/500000,1),0)+IF(ISNUMBER(C20),MIN(C20/60,1),0)+IF(ISNUMBER(D20),D20/5,0)+IF(ISNUMBER(E20),E20/5,0)+IF(F20="да",1,0)+IF(G20="да",1,0)+IF(ISNUMBER(H20),MIN(H20/50,1),0)+IF(ISNUMBER(I20),MIN(I20/6,1),0)+IF(ISNUMBER(J20),IF(J20&gt;0,1,0),0))/MAX(1,ISNUMBER(B20)+ISNUMBER(C20)+ISNUMBER(D20)+ISNUMBER(E20)+(F20&lt;&gt;"")+(G20&lt;&gt;"")+ISNUMBER(H20)+ISNUMBER(I20)+ISNUMBER(J20))))</f>
         <v/>
       </c>
       <c r="L20" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K20="","",IF(K20&gt;=0.7,5,IF(K20&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M20" s="2"/>
@@ -7053,11 +7052,11 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B21:J21)=0,"",MIN(1,(IF(ISNUMBER(B21),MIN(B21/500000,1),0)+IF(ISNUMBER(C21),MIN(C21/60,1),0)+IF(ISNUMBER(D21),D21/5,0)+IF(ISNUMBER(E21),E21/5,0)+IF(F21="да",1,0)+IF(G21="да",1,0)+IF(ISNUMBER(H21),MIN(H21/50,1),0)+IF(ISNUMBER(I21),MIN(I21/6,1),0)+IF(ISNUMBER(J21),IF(J21&gt;0,1,0),0))/MAX(1,ISNUMBER(B21)+ISNUMBER(C21)+ISNUMBER(D21)+ISNUMBER(E21)+(F21&lt;&gt;"")+(G21&lt;&gt;"")+ISNUMBER(H21)+ISNUMBER(I21)+ISNUMBER(J21))))</f>
         <v/>
       </c>
       <c r="L21" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K21="","",IF(K21&gt;=0.7,5,IF(K21&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M21" s="2"/>
@@ -7074,11 +7073,11 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B22:J22)=0,"",MIN(1,(IF(ISNUMBER(B22),MIN(B22/500000,1),0)+IF(ISNUMBER(C22),MIN(C22/60,1),0)+IF(ISNUMBER(D22),D22/5,0)+IF(ISNUMBER(E22),E22/5,0)+IF(F22="да",1,0)+IF(G22="да",1,0)+IF(ISNUMBER(H22),MIN(H22/50,1),0)+IF(ISNUMBER(I22),MIN(I22/6,1),0)+IF(ISNUMBER(J22),IF(J22&gt;0,1,0),0))/MAX(1,ISNUMBER(B22)+ISNUMBER(C22)+ISNUMBER(D22)+ISNUMBER(E22)+(F22&lt;&gt;"")+(G22&lt;&gt;"")+ISNUMBER(H22)+ISNUMBER(I22)+ISNUMBER(J22))))</f>
         <v/>
       </c>
       <c r="L22" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K22="","",IF(K22&gt;=0.7,5,IF(K22&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M22" s="2"/>
@@ -7095,11 +7094,11 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B23:J23)=0,"",MIN(1,(IF(ISNUMBER(B23),MIN(B23/500000,1),0)+IF(ISNUMBER(C23),MIN(C23/60,1),0)+IF(ISNUMBER(D23),D23/5,0)+IF(ISNUMBER(E23),E23/5,0)+IF(F23="да",1,0)+IF(G23="да",1,0)+IF(ISNUMBER(H23),MIN(H23/50,1),0)+IF(ISNUMBER(I23),MIN(I23/6,1),0)+IF(ISNUMBER(J23),IF(J23&gt;0,1,0),0))/MAX(1,ISNUMBER(B23)+ISNUMBER(C23)+ISNUMBER(D23)+ISNUMBER(E23)+(F23&lt;&gt;"")+(G23&lt;&gt;"")+ISNUMBER(H23)+ISNUMBER(I23)+ISNUMBER(J23))))</f>
         <v/>
       </c>
       <c r="L23" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K23="","",IF(K23&gt;=0.7,5,IF(K23&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M23" s="2"/>
@@ -7116,11 +7115,11 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B24:J24)=0,"",MIN(1,(IF(ISNUMBER(B24),MIN(B24/500000,1),0)+IF(ISNUMBER(C24),MIN(C24/60,1),0)+IF(ISNUMBER(D24),D24/5,0)+IF(ISNUMBER(E24),E24/5,0)+IF(F24="да",1,0)+IF(G24="да",1,0)+IF(ISNUMBER(H24),MIN(H24/50,1),0)+IF(ISNUMBER(I24),MIN(I24/6,1),0)+IF(ISNUMBER(J24),IF(J24&gt;0,1,0),0))/MAX(1,ISNUMBER(B24)+ISNUMBER(C24)+ISNUMBER(D24)+ISNUMBER(E24)+(F24&lt;&gt;"")+(G24&lt;&gt;"")+ISNUMBER(H24)+ISNUMBER(I24)+ISNUMBER(J24))))</f>
         <v/>
       </c>
       <c r="L24" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K24="","",IF(K24&gt;=0.7,5,IF(K24&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M24" s="2"/>
@@ -7137,11 +7136,11 @@
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B25:J25)=0,"",MIN(1,(IF(ISNUMBER(B25),MIN(B25/500000,1),0)+IF(ISNUMBER(C25),MIN(C25/60,1),0)+IF(ISNUMBER(D25),D25/5,0)+IF(ISNUMBER(E25),E25/5,0)+IF(F25="да",1,0)+IF(G25="да",1,0)+IF(ISNUMBER(H25),MIN(H25/50,1),0)+IF(ISNUMBER(I25),MIN(I25/6,1),0)+IF(ISNUMBER(J25),IF(J25&gt;0,1,0),0))/MAX(1,ISNUMBER(B25)+ISNUMBER(C25)+ISNUMBER(D25)+ISNUMBER(E25)+(F25&lt;&gt;"")+(G25&lt;&gt;"")+ISNUMBER(H25)+ISNUMBER(I25)+ISNUMBER(J25))))</f>
         <v/>
       </c>
       <c r="L25" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K25="","",IF(K25&gt;=0.7,5,IF(K25&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M25" s="2"/>
@@ -7158,11 +7157,11 @@
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="K26" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B26:J26)=0,"",MIN(1,(IF(ISNUMBER(B26),MIN(B26/500000,1),0)+IF(ISNUMBER(C26),MIN(C26/60,1),0)+IF(ISNUMBER(D26),D26/5,0)+IF(ISNUMBER(E26),E26/5,0)+IF(F26="да",1,0)+IF(G26="да",1,0)+IF(ISNUMBER(H26),MIN(H26/50,1),0)+IF(ISNUMBER(I26),MIN(I26/6,1),0)+IF(ISNUMBER(J26),IF(J26&gt;0,1,0),0))/MAX(1,ISNUMBER(B26)+ISNUMBER(C26)+ISNUMBER(D26)+ISNUMBER(E26)+(F26&lt;&gt;"")+(G26&lt;&gt;"")+ISNUMBER(H26)+ISNUMBER(I26)+ISNUMBER(J26))))</f>
         <v/>
       </c>
       <c r="L26" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K26="","",IF(K26&gt;=0.7,5,IF(K26&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M26" s="2"/>
@@ -7179,11 +7178,11 @@
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B27:J27)=0,"",MIN(1,(IF(ISNUMBER(B27),MIN(B27/500000,1),0)+IF(ISNUMBER(C27),MIN(C27/60,1),0)+IF(ISNUMBER(D27),D27/5,0)+IF(ISNUMBER(E27),E27/5,0)+IF(F27="да",1,0)+IF(G27="да",1,0)+IF(ISNUMBER(H27),MIN(H27/50,1),0)+IF(ISNUMBER(I27),MIN(I27/6,1),0)+IF(ISNUMBER(J27),IF(J27&gt;0,1,0),0))/MAX(1,ISNUMBER(B27)+ISNUMBER(C27)+ISNUMBER(D27)+ISNUMBER(E27)+(F27&lt;&gt;"")+(G27&lt;&gt;"")+ISNUMBER(H27)+ISNUMBER(I27)+ISNUMBER(J27))))</f>
         <v/>
       </c>
       <c r="L27" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K27="","",IF(K27&gt;=0.7,5,IF(K27&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M27" s="2"/>
@@ -7200,11 +7199,11 @@
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B28:J28)=0,"",MIN(1,(IF(ISNUMBER(B28),MIN(B28/500000,1),0)+IF(ISNUMBER(C28),MIN(C28/60,1),0)+IF(ISNUMBER(D28),D28/5,0)+IF(ISNUMBER(E28),E28/5,0)+IF(F28="да",1,0)+IF(G28="да",1,0)+IF(ISNUMBER(H28),MIN(H28/50,1),0)+IF(ISNUMBER(I28),MIN(I28/6,1),0)+IF(ISNUMBER(J28),IF(J28&gt;0,1,0),0))/MAX(1,ISNUMBER(B28)+ISNUMBER(C28)+ISNUMBER(D28)+ISNUMBER(E28)+(F28&lt;&gt;"")+(G28&lt;&gt;"")+ISNUMBER(H28)+ISNUMBER(I28)+ISNUMBER(J28))))</f>
         <v/>
       </c>
       <c r="L28" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K28="","",IF(K28&gt;=0.7,5,IF(K28&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M28" s="2"/>
@@ -7221,11 +7220,11 @@
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="K29" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B29:J29)=0,"",MIN(1,(IF(ISNUMBER(B29),MIN(B29/500000,1),0)+IF(ISNUMBER(C29),MIN(C29/60,1),0)+IF(ISNUMBER(D29),D29/5,0)+IF(ISNUMBER(E29),E29/5,0)+IF(F29="да",1,0)+IF(G29="да",1,0)+IF(ISNUMBER(H29),MIN(H29/50,1),0)+IF(ISNUMBER(I29),MIN(I29/6,1),0)+IF(ISNUMBER(J29),IF(J29&gt;0,1,0),0))/MAX(1,ISNUMBER(B29)+ISNUMBER(C29)+ISNUMBER(D29)+ISNUMBER(E29)+(F29&lt;&gt;"")+(G29&lt;&gt;"")+ISNUMBER(H29)+ISNUMBER(I29)+ISNUMBER(J29))))</f>
         <v/>
       </c>
       <c r="L29" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K29="","",IF(K29&gt;=0.7,5,IF(K29&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M29" s="2"/>
@@ -7242,11 +7241,11 @@
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B30:J30)=0,"",MIN(1,(IF(ISNUMBER(B30),MIN(B30/500000,1),0)+IF(ISNUMBER(C30),MIN(C30/60,1),0)+IF(ISNUMBER(D30),D30/5,0)+IF(ISNUMBER(E30),E30/5,0)+IF(F30="да",1,0)+IF(G30="да",1,0)+IF(ISNUMBER(H30),MIN(H30/50,1),0)+IF(ISNUMBER(I30),MIN(I30/6,1),0)+IF(ISNUMBER(J30),IF(J30&gt;0,1,0),0))/MAX(1,ISNUMBER(B30)+ISNUMBER(C30)+ISNUMBER(D30)+ISNUMBER(E30)+(F30&lt;&gt;"")+(G30&lt;&gt;"")+ISNUMBER(H30)+ISNUMBER(I30)+ISNUMBER(J30))))</f>
         <v/>
       </c>
       <c r="L30" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K30="","",IF(K30&gt;=0.7,5,IF(K30&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M30" s="2"/>
@@ -7263,11 +7262,11 @@
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B31:J31)=0,"",MIN(1,(IF(ISNUMBER(B31),MIN(B31/500000,1),0)+IF(ISNUMBER(C31),MIN(C31/60,1),0)+IF(ISNUMBER(D31),D31/5,0)+IF(ISNUMBER(E31),E31/5,0)+IF(F31="да",1,0)+IF(G31="да",1,0)+IF(ISNUMBER(H31),MIN(H31/50,1),0)+IF(ISNUMBER(I31),MIN(I31/6,1),0)+IF(ISNUMBER(J31),IF(J31&gt;0,1,0),0))/MAX(1,ISNUMBER(B31)+ISNUMBER(C31)+ISNUMBER(D31)+ISNUMBER(E31)+(F31&lt;&gt;"")+(G31&lt;&gt;"")+ISNUMBER(H31)+ISNUMBER(I31)+ISNUMBER(J31))))</f>
         <v/>
       </c>
       <c r="L31" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K31="","",IF(K31&gt;=0.7,5,IF(K31&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M31" s="2"/>
@@ -7284,11 +7283,11 @@
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B32:J32)=0,"",MIN(1,(IF(ISNUMBER(B32),MIN(B32/500000,1),0)+IF(ISNUMBER(C32),MIN(C32/60,1),0)+IF(ISNUMBER(D32),D32/5,0)+IF(ISNUMBER(E32),E32/5,0)+IF(F32="да",1,0)+IF(G32="да",1,0)+IF(ISNUMBER(H32),MIN(H32/50,1),0)+IF(ISNUMBER(I32),MIN(I32/6,1),0)+IF(ISNUMBER(J32),IF(J32&gt;0,1,0),0))/MAX(1,ISNUMBER(B32)+ISNUMBER(C32)+ISNUMBER(D32)+ISNUMBER(E32)+(F32&lt;&gt;"")+(G32&lt;&gt;"")+ISNUMBER(H32)+ISNUMBER(I32)+ISNUMBER(J32))))</f>
         <v/>
       </c>
       <c r="L32" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K32="","",IF(K32&gt;=0.7,5,IF(K32&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M32" s="2"/>
@@ -7305,11 +7304,11 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(COUNTA(B33:J33)=0,"",MIN(1,(IF(ISNUMBER(B33),MIN(B33/500000,1),0)+IF(ISNUMBER(C33),MIN(C33/60,1),0)+IF(ISNUMBER(D33),D33/5,0)+IF(ISNUMBER(E33),E33/5,0)+IF(F33="да",1,0)+IF(G33="да",1,0)+IF(ISNUMBER(H33),MIN(H33/50,1),0)+IF(ISNUMBER(I33),MIN(I33/6,1),0)+IF(ISNUMBER(J33),IF(J33&gt;0,1,0),0))/MAX(1,ISNUMBER(B33)+ISNUMBER(C33)+ISNUMBER(D33)+ISNUMBER(E33)+(F33&lt;&gt;"")+(G33&lt;&gt;"")+ISNUMBER(H33)+ISNUMBER(I33)+ISNUMBER(J33))))</f>
         <v/>
       </c>
       <c r="L33" s="18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(K33="","",IF(K33&gt;=0.7,5,IF(K33&gt;=0.4,3,1)))</f>
         <v/>
       </c>
       <c r="M33" s="2"/>
@@ -7404,30 +7403,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -7595,7 +7594,7 @@
         <v>251</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C8" s="9">
         <f>IF(ISNUMBER('04_Поиск_реклама'!B37),'04_Поиск_реклама'!B37,AVERAGE(MIN('03_Каналы_трафика'!C5/'01_Параметры'!B15,1),MIN('03_Каналы_трафика'!C6/'01_Параметры'!B14,1)))</f>
@@ -7694,7 +7693,7 @@
         <v>262</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C11" s="11">
         <v>0.6</v>
@@ -7726,7 +7725,7 @@
         <v>265</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C12" s="11">
         <f>IFERROR(1-SUMPRODUCT(('02_Конкуренты_SW'!B4:B33&lt;&gt;"")*(LEFT('02_Конкуренты_SW'!B4:B33,6)="прямой")*'02_Конкуренты_SW'!E4:E33)/SUM('02_Конкуренты_SW'!E4:E33),0)</f>
@@ -7779,7 +7778,7 @@
         <v>средние барьеры</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>269</v>
@@ -7835,36 +7834,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>270</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
     </row>
     <row r="2" spans="1:12" ht="16.05" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="17" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -8127,51 +8126,51 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="14" customHeight="1">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="29" t="str">
+      <c r="A15" s="28" t="str">
         <f>"По результатам оценки цифровой конкуренции индекс барьеров входа составляет "&amp;ROUND(B5,2)&amp;" из 5, что соответствует уровню: "&amp;B6&amp;". "&amp;"Наиболее значимые факторы давления определены по листу 07_Барьеры_входа. "&amp;"Данные Similarweb и альтернативных источников являются оценочной базой и требуют проверки "&amp;"через фактические коммерческие данные, цены, конверсии и платежеспособность клиентов."</f>
         <v>По результатам оценки цифровой конкуренции индекс барьеров входа составляет 3,15 из 5, что соответствует уровню: средние барьеры. Наиболее значимые факторы давления определены по листу 07_Барьеры_входа. Данные Similarweb и альтернативных источников являются оценочной базой и требуют проверки через фактические коммерческие данные, цены, конверсии и платежеспособность клиентов.</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="29"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="4">
